--- a/_qa/Generator_Tests.xlsx
+++ b/_qa/Generator_Tests.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="676">
   <si>
     <t>Test ID</t>
   </si>
@@ -1082,19 +1082,1705 @@
   </si>
   <si>
     <t>Editor navigates to or highlights the problematic generator</t>
+  </si>
+  <si>
+    <t>Navigate to Basic Settings tab</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Click on any Generator shape (oval/ellipse) in the diagram
+3. The right panel shows "Generator Editor" at the top</t>
+  </si>
+  <si>
+    <t>1. Look at the tab bar at the top of the Generator Editor panel
+2. Find the GEAR icon (⚙️) - it's the first icon on the left
+3. Click the gear icon
+4. Wait for the content below to update</t>
+  </si>
+  <si>
+    <t>1. The gear icon appears highlighted or selected
+2. Below the tab bar, you see "Basic Settings" content:
+   - A "Generator Name" text box near the top
+   - A "Generator Type" dropdown (Frequency-Based or Time-Distributed)
+   - An "Entity" dropdown to select which entity type to generate</t>
+  </si>
+  <si>
+    <t>Navigate to Frequency Settings tab</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected
+2. The Generator Type is set to "Frequency-Based"
+3. The Generator Editor panel is visible</t>
+  </si>
+  <si>
+    <t>1. Look at the tab bar at the top of the Generator Editor panel
+2. Find the CLOCK/TIMER icon (⏱️) - it appears when type is Frequency-Based
+3. Click the clock/frequency icon
+4. Wait for the content below to update</t>
+  </si>
+  <si>
+    <t>1. The frequency icon appears highlighted or selected
+2. Below the tab bar, you see "Frequency Settings" content:
+   - Time Between Arrivals fields (value and unit)
+   - Periodic Occurrences field
+   - Entities Per Creation field
+   - Max Entities field
+   - Start Delay field</t>
+  </si>
+  <si>
+    <t>Only visible when Generator Type = Frequency-Based</t>
+  </si>
+  <si>
+    <t>Navigate to Time Distribution tab</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected
+2. The Generator Type is set to "Time-Distributed"
+3. The Generator Editor panel is visible</t>
+  </si>
+  <si>
+    <t>1. Look at the tab bar at the top of the Generator Editor panel
+2. Find the CHART/DISTRIBUTION icon (📊) - it appears when type is Time-Distributed
+3. Click the distribution icon
+4. Wait for the content below to update</t>
+  </si>
+  <si>
+    <t>1. The distribution icon appears highlighted or selected
+2. Below the tab bar, you see "Time Distribution" content:
+   - Time Patterns section with Add Pattern button
+   - Distribution Configs section with Add Config button
+   - Checkboxes to associate configs with this generator</t>
+  </si>
+  <si>
+    <t>Only visible when Generator Type = Time-Distributed</t>
+  </si>
+  <si>
+    <t>Navigate to Events tab (State Modifications)</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected
+2. The Generator Editor panel is visible
+3. At least one State is defined in the model</t>
+  </si>
+  <si>
+    <t>1. Look at the tab bar at the top of the Generator Editor panel
+2. Find the LIGHTNING/EVENT icon (⚡) - usually 3rd or 4th tab
+3. Click the events icon
+4. Wait for the content below to update</t>
+  </si>
+  <si>
+    <t>1. The events icon appears highlighted or selected
+2. Below the tab bar, you see "State Modifications" content:
+   - A list of initial state values that can be set on generated entities
+   - Options to add/edit/delete state modifications
+   - Each modification shows state name and value</t>
+  </si>
+  <si>
+    <t>Sets initial state values on newly generated entities</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected
+2. The Generator Editor panel is visible</t>
+  </si>
+  <si>
+    <t>1. Look at the tab bar at the top of the Generator Editor panel
+2. Find the STATES/LIST icon - usually the last tab
+3. Click the states icon
+4. Wait for the content below to update</t>
+  </si>
+  <si>
+    <t>1. The states icon appears highlighted or selected
+2. Below the tab bar, you see "States" editor content:
+   - A list of states that can be defined
+   - Add/Edit/Delete options for states
+   - NOTE: Save/Cancel buttons may be HIDDEN on this tab (auto-save)</t>
+  </si>
+  <si>
+    <t>States tab uses auto-save - no Save button needed</t>
+  </si>
+  <si>
+    <t>Tab visibility changes - Frequency-Based mode</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected
+2. Go to Basic Settings tab (gear icon)
+3. Note which tabs are currently visible</t>
+  </si>
+  <si>
+    <t>1. In the Basic Settings, find the "Generator Type" dropdown
+2. Click the dropdown
+3. Select "Frequency-Based" from the options
+4. Look at the tab bar to see which tabs are now visible</t>
+  </si>
+  <si>
+    <t>1. The Generator Type changes to Frequency-Based
+2. The tab bar updates:
+   - FREQUENCY tab icon becomes VISIBLE (clock/timer icon)
+   - DISTRIBUTION tab icon becomes HIDDEN
+3. The available tabs are now: Basic, Frequency, Events, States
+4. The Save button becomes blue/clickable</t>
+  </si>
+  <si>
+    <t>Frequency and Distribution tabs are mutually exclusive</t>
+  </si>
+  <si>
+    <t>Tab visibility changes - Time-Distributed mode</t>
+  </si>
+  <si>
+    <t>1. In the Basic Settings, find the "Generator Type" dropdown
+2. Click the dropdown
+3. Select "Time-Distributed" from the options
+4. Look at the tab bar to see which tabs are now visible</t>
+  </si>
+  <si>
+    <t>1. The Generator Type changes to Time-Distributed
+2. The tab bar updates:
+   - DISTRIBUTION tab icon becomes VISIBLE (chart icon)
+   - FREQUENCY tab icon becomes HIDDEN
+3. The available tabs are now: Basic, Distribution, Events, States
+4. The Save button becomes blue/clickable</t>
+  </si>
+  <si>
+    <t>Auto-switch tab when type changes</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected with type = Frequency-Based
+2. You are currently ON the Frequency Settings tab
+3. The Frequency tab content is visible</t>
+  </si>
+  <si>
+    <t>1. While on the Frequency tab, switch to Basic Settings (gear icon)
+2. Change the Generator Type dropdown to "Time-Distributed"
+3. Observe which tab becomes active</t>
+  </si>
+  <si>
+    <t>1. Since the Frequency tab is no longer valid for Time-Distributed type:
+   - The UI automatically switches to a valid tab
+   - Either stays on Basic Settings OR switches to Distribution tab
+2. The Frequency tab icon disappears from the tab bar
+3. The Distribution tab icon appears
+4. You are NOT left on a hidden/invalid tab</t>
+  </si>
+  <si>
+    <t>UI prevents being stuck on an invalid tab</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Click on any Generator shape (oval/ellipse) in the diagram
+3. The Generator Editor panel shows on the right
+4. The Basic Settings tab (gear icon) is selected</t>
+  </si>
+  <si>
+    <t>1. Find the "Generator Name" text box near the top of the panel
+2. Click inside the text box - you'll see a blinking cursor
+3. Select all existing text (Ctrl+A or triple-click)
+4. Type a new name like "Customer Arrivals"
+5. Press Tab or click somewhere else outside the text box</t>
+  </si>
+  <si>
+    <t>1. The text box now displays your new name "Customer Arrivals"
+2. Look at the bottom of the panel
+3. The "Save" button should now be BLUE and clickable (not grayed out)
+4. A "Cancel" button appears next to Save</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected
+2. The Basic Settings tab (gear icon) is selected
+3. The Generator Name field currently has text in it</t>
+  </si>
+  <si>
+    <t>1. Find the "Generator Name" text box near the top
+2. Click inside the text box
+3. Select all text (Ctrl+A)
+4. Press Delete or Backspace to clear it completely
+5. Press Tab or click outside the field</t>
+  </si>
+  <si>
+    <t>1. The Generator Name field is now empty
+2. The system should either:
+   a) Show an error/warning message (e.g., "Name required"), OR
+   b) Accept the empty name (validation may warn later)
+3. Check if the Save button is enabled or disabled
+4. Document the actual behavior observed</t>
+  </si>
+  <si>
+    <t>Test whether empty names are allowed or trigger validation</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected
+2. The Basic Settings tab (gear icon) is selected</t>
+  </si>
+  <si>
+    <t>1. Find the "Generator Name" text box
+2. Click inside and clear any existing text
+3. Type a name with special characters: "Test!@#$%^&amp;*()Gen"
+4. Press Tab or click outside the field
+5. Try to Save the changes</t>
+  </si>
+  <si>
+    <t>1. The field accepts the special characters
+2. All typed characters are displayed
+3. The Save button becomes blue/clickable
+4. After saving, the name persists with special characters
+5. No errors occur (unless specific characters are restricted)</t>
+  </si>
+  <si>
+    <t>Tests special character handling in names</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected
+2. The Basic Settings tab (gear icon) is selected
+3. Note the current Generator Type (Frequency-Based or Time-Distributed)</t>
+  </si>
+  <si>
+    <t>1. Find the "Generator Type" dropdown in the Basic Settings
+2. Click on the dropdown to open it
+3. You'll see two options:
+   - Frequency-Based
+   - Time-Distributed
+4. Select the OPPOSITE type from what's currently shown
+5. Observe the changes in the tab bar</t>
+  </si>
+  <si>
+    <t>1. The Generator Type dropdown shows your new selection
+2. The tab bar at the top CHANGES:
+   - If you selected Frequency-Based: Frequency tab appears, Distribution tab disappears
+   - If you selected Time-Distributed: Distribution tab appears, Frequency tab disappears
+3. The Save button becomes blue/clickable
+4. The UI updates smoothly without errors</t>
+  </si>
+  <si>
+    <t>Generator type determines which settings tabs are available</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected
+2. The Basic Settings tab (gear icon) is selected
+3. At least 2 Entity types exist in the model</t>
+  </si>
+  <si>
+    <t>1. Find the "Entity" dropdown in the Basic Settings
+2. Click on the dropdown to open it
+3. You'll see a list of available entity types from the model
+4. Select a DIFFERENT entity type than currently selected
+5. Observe the changes</t>
+  </si>
+  <si>
+    <t>1. The Entity dropdown now shows your new selection
+2. The Save button becomes blue/clickable
+3. This entity type is what the generator will create
+4. After saving, the generator produces entities of this new type</t>
+  </si>
+  <si>
+    <t>Entity determines what type of entities are generated</t>
+  </si>
+  <si>
+    <t>Entity dropdown shows all model entities</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document with a Quodsi model
+2. The model has multiple Entity types defined (e.g., "Customer", "Order", "Product")
+3. Select a Generator in the diagram</t>
+  </si>
+  <si>
+    <t>1. Go to the Basic Settings tab (gear icon)
+2. Find the "Entity" dropdown
+3. Click on the dropdown to open it
+4. Look at all the options listed
+5. Compare with the entities defined in your model</t>
+  </si>
+  <si>
+    <t>1. The dropdown shows ALL entity types from the model
+2. Each entity type you've defined should appear as an option
+3. The list should match exactly what's defined in the model
+4. If no entities exist, the dropdown may be empty or show a message
+5. Entities are not duplicated in the list</t>
+  </si>
+  <si>
+    <t>Verifies entity dropdown is properly populated</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected with type = Frequency-Based
+2. Click the Frequency Settings tab (clock/timer icon)
+3. The Frequency Settings content is visible</t>
+  </si>
+  <si>
+    <t>1. Find the "Time Between Arrivals" section
+2. Look for the numeric value field (e.g., shows "5" or another number)
+3. Click inside the value field
+4. Clear the existing value and type 10
+5. Press Tab or click outside the field</t>
+  </si>
+  <si>
+    <t>1. The value field now shows "10"
+2. The Save button at the bottom becomes blue/clickable
+3. No error messages appear
+4. This means entities will be generated every 10 time units</t>
+  </si>
+  <si>
+    <t>Controls how often entities are generated</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected with type = Frequency-Based
+2. The Frequency Settings tab is open
+3. The Time Between Arrivals section is visible</t>
+  </si>
+  <si>
+    <t>1. Find the "Time Between Arrivals" section
+2. Look for the time UNIT dropdown (e.g., "Minutes", "Hours", "Seconds")
+3. Click the dropdown to open it
+4. Select a different unit (e.g., change from Minutes to Hours)
+5. Observe the change</t>
+  </si>
+  <si>
+    <t>1. The unit dropdown now shows your selection (e.g., "Hours")
+2. The Save button becomes blue/clickable
+3. The VALUE remains the same, only the unit changes
+4. Example: "5 Minutes" becomes "5 Hours" - a significant difference!</t>
+  </si>
+  <si>
+    <t>Time units: Seconds, Minutes, Hours, Days, etc.</t>
+  </si>
+  <si>
+    <t>1. Find the "Distribution" dropdown in Time Between Arrivals
+2. The default is usually "Constant"
+3. Click the dropdown to open it
+4. Select a different distribution (e.g., "Exponential", "Normal", "Uniform")
+5. Observe how the input fields change</t>
+  </si>
+  <si>
+    <t>1. The distribution type changes to your selection
+2. The input fields may CHANGE based on distribution:
+   - Constant: single value field
+   - Exponential: mean value field
+   - Uniform: min and max value fields
+   - Normal: mean and standard deviation fields
+3. The Save button becomes blue/clickable</t>
+  </si>
+  <si>
+    <t>Different distributions have different parameter fields</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected with type = Frequency-Based
+2. The Frequency Settings tab is open</t>
+  </si>
+  <si>
+    <t>1. Find the "Periodic Occurrences" field
+2. This controls how many times the generator will produce batches of entities
+3. Click inside the field
+4. Clear the existing value and type 100
+5. Press Tab or click outside the field</t>
+  </si>
+  <si>
+    <t>1. The field now shows "100"
+2. The Save button becomes blue/clickable
+3. This means the generator will run 100 cycles/occurrences
+4. After 100 occurrences, the generator stops</t>
+  </si>
+  <si>
+    <t>Limits total number of generation events</t>
+  </si>
+  <si>
+    <t>Infinite occurrences (999999)</t>
+  </si>
+  <si>
+    <t>1. Find the "Periodic Occurrences" field
+2. Click inside the field
+3. Clear the existing value
+4. Type 999999 (six 9s)
+5. Press Tab or click outside the field</t>
+  </si>
+  <si>
+    <t>1. The field accepts 999999 as a valid value
+2. The Save button becomes blue/clickable
+3. 999999 represents "unlimited" or "infinite" occurrences
+4. The generator will run indefinitely (until simulation ends or max entities reached)</t>
+  </si>
+  <si>
+    <t>999999 = unlimited occurrences convention</t>
+  </si>
+  <si>
+    <t>1. Find the "Periodic Occurrences" field
+2. Click inside the field
+3. Clear the existing value
+4. Type 0 (zero)
+5. Press Tab or click outside the field
+6. Try to Save</t>
+  </si>
+  <si>
+    <t>1. The system should either:
+   a) Accept 0 (generator will never produce anything), OR
+   b) Show a validation warning/error
+2. Document the actual behavior
+3. Zero occurrences means the generator is effectively disabled</t>
+  </si>
+  <si>
+    <t>Edge case - zero means no generation</t>
+  </si>
+  <si>
+    <t>1. Find the "Start Delay" field section
+2. This controls when the generator begins producing entities
+3. Click inside the value field
+4. Clear the existing value and type 30
+5. Press Tab or click outside the field</t>
+  </si>
+  <si>
+    <t>1. The Start Delay field shows "30"
+2. The Save button becomes blue/clickable
+3. The generator will wait 30 time units before first generation
+4. You can also change the time unit if needed</t>
+  </si>
+  <si>
+    <t>Delays when generator starts producing</t>
+  </si>
+  <si>
+    <t>1. Find the "Entities Per Creation" field
+2. This controls how many entities are created each time
+3. Click inside the field
+4. Clear the existing value and type 5
+5. Press Tab or click outside the field</t>
+  </si>
+  <si>
+    <t>1. The field now shows "5"
+2. The Save button becomes blue/clickable
+3. Each generation event will now create 5 entities at once
+4. Valid range is typically 1-1000</t>
+  </si>
+  <si>
+    <t>Batch size for each generation event</t>
+  </si>
+  <si>
+    <t>1. Find the "Max Entities" field
+2. This controls the maximum total entities this generator can create
+3. Click inside the field
+4. Clear the existing value and type 1000
+5. Press Tab or click outside the field</t>
+  </si>
+  <si>
+    <t>1. The field now shows "1000"
+2. The Save button becomes blue/clickable
+3. The generator will stop after creating 1000 total entities
+4. Even if occurrences would allow more, it stops at max</t>
+  </si>
+  <si>
+    <t>Total entity limit across all generation events</t>
+  </si>
+  <si>
+    <t>1. Find any numeric field (e.g., Periodic Occurrences, Time Between Arrivals, Entities Per Creation)
+2. Click inside the field
+3. Clear the existing value
+4. Type -1 (negative one)
+5. Press Tab or click outside the field
+6. Try to Save</t>
+  </si>
+  <si>
+    <t>1. The system should either:
+   a) Reject the negative value immediately (field validation)
+   b) Show a validation error when trying to save
+2. Negative values are not valid for frequency settings
+3. The Save button should be disabled if there's an error
+4. Document which fields allow/reject negatives</t>
+  </si>
+  <si>
+    <t>Negative values should be rejected</t>
+  </si>
+  <si>
+    <t>Add new time pattern</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected with type = Time-Distributed
+2. Click the Time Distribution tab (chart icon)
+3. The Time Distribution content is visible</t>
+  </si>
+  <si>
+    <t>1. Find the "Time Patterns" section in the panel
+2. Look for the "+ Add Pattern" or "Add" button
+3. Click the Add Pattern button
+4. Wait for a modal/dialog to appear</t>
+  </si>
+  <si>
+    <t>1. A modal (popup window) opens
+2. The modal shows fields to configure a time pattern:
+   - Pattern name or identifier
+   - Time range/period settings
+   - Generation rate or quantity settings
+3. You can configure when and how many entities to generate
+4. Save/Cancel buttons are available in the modal</t>
+  </si>
+  <si>
+    <t>Time patterns define WHEN entities are generated</t>
+  </si>
+  <si>
+    <t>Edit existing time pattern</t>
+  </si>
+  <si>
+    <t>1. Have a Generator with type = Time-Distributed
+2. At least one time pattern already exists
+3. The Time Distribution tab is open</t>
+  </si>
+  <si>
+    <t>1. Find the "Time Patterns" section
+2. Look at the list of existing patterns
+3. Find the pattern you want to edit
+4. Click the "Edit" button or pencil icon next to that pattern
+5. Wait for the modal to open</t>
+  </si>
+  <si>
+    <t>1. A modal opens showing the pattern's current settings
+2. All fields are pre-filled with the existing values
+3. You can modify any of the values
+4. Save/Cancel buttons are available
+5. After saving, the pattern list shows updated values</t>
+  </si>
+  <si>
+    <t>1. Have a Generator with type = Time-Distributed
+2. At least one time pattern exists
+3. The Time Distribution tab is open</t>
+  </si>
+  <si>
+    <t>1. Find the "Time Patterns" section
+2. Look at the list of existing patterns
+3. Find the pattern you want to delete
+4. Click the "Delete" button or trash icon next to that pattern
+5. If a confirmation dialog appears, click "Yes" or "Confirm"</t>
+  </si>
+  <si>
+    <t>1. The pattern is removed from the list
+2. The pattern no longer appears in Time Patterns
+3. The Save button may become blue/clickable
+4. Confirm by saving and reopening - pattern should be gone</t>
+  </si>
+  <si>
+    <t>Deleting may require confirmation</t>
+  </si>
+  <si>
+    <t>Cancel delete time pattern</t>
+  </si>
+  <si>
+    <t>1. Find a pattern in the Time Patterns section
+2. Click the Delete button for that pattern
+3. When the confirmation dialog appears, click "Cancel" or "No"
+4. Check the pattern list</t>
+  </si>
+  <si>
+    <t>1. The confirmation dialog closes
+2. The pattern is NOT deleted - it still appears in the list
+3. Clicking Cancel prevents deletion
+4. No changes are made to the pattern</t>
+  </si>
+  <si>
+    <t>Tests cancellation of destructive action</t>
+  </si>
+  <si>
+    <t>Add new distribution config</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected with type = Time-Distributed
+2. The Time Distribution tab is open</t>
+  </si>
+  <si>
+    <t>1. Find the "Distribution Configs" section (separate from Time Patterns)
+2. Look for the "+ Add Config" or "Add" button
+3. Click the Add Config button
+4. Wait for a modal/dialog to appear</t>
+  </si>
+  <si>
+    <t>1. A modal opens for configuring a distribution
+2. The modal shows fields such as:
+   - Config name
+   - Distribution type (Constant, Exponential, etc.)
+   - Distribution parameters (based on type)
+3. Save/Cancel buttons are available
+4. After saving, the new config appears in the list</t>
+  </si>
+  <si>
+    <t>Configs define HOW MANY entities per time slot</t>
+  </si>
+  <si>
+    <t>Edit existing distribution config</t>
+  </si>
+  <si>
+    <t>1. Have a Generator with type = Time-Distributed
+2. At least one distribution config exists
+3. The Time Distribution tab is open</t>
+  </si>
+  <si>
+    <t>1. Find the "Distribution Configs" section
+2. Look at the list of existing configs
+3. Find the config you want to edit
+4. Click the "Edit" button or pencil icon next to that config
+5. Wait for the modal to open</t>
+  </si>
+  <si>
+    <t>1. A modal opens showing the config's current settings
+2. All fields are pre-filled with existing values
+3. You can modify the distribution type and parameters
+4. Save/Cancel buttons are available
+5. After saving, the config list shows updated values</t>
+  </si>
+  <si>
+    <t>1. Have a Generator with type = Time-Distributed
+2. At least one distribution config exists
+3. The config is NOT currently associated with this generator (unchecked)</t>
+  </si>
+  <si>
+    <t>1. Find the "Distribution Configs" section
+2. Look at the list of existing configs
+3. Find the config you want to delete
+4. Click the "Delete" button or trash icon next to that config
+5. Confirm deletion if prompted</t>
+  </si>
+  <si>
+    <t>1. The config is removed from the list
+2. The config no longer appears in Distribution Configs
+3. NOTE: You may not be able to delete a config that's currently in use
+4. Document any restrictions on deleting in-use configs</t>
+  </si>
+  <si>
+    <t>May be restricted if config is in use</t>
+  </si>
+  <si>
+    <t>Associate config with generator (check)</t>
+  </si>
+  <si>
+    <t>1. Have a Generator with type = Time-Distributed
+2. At least one distribution config exists
+3. The config is currently UNCHECKED (not associated)</t>
+  </si>
+  <si>
+    <t>1. Find the "Distribution Configs" section
+2. Look at the list of configs - each should have a checkbox
+3. Find a config that is currently UNCHECKED
+4. Click the checkbox to CHECK it
+5. Observe the changes</t>
+  </si>
+  <si>
+    <t>1. The checkbox becomes checked (✓)
+2. The config is now associated with this generator
+3. The Save button becomes blue/clickable
+4. After saving, this config will be used by the generator</t>
+  </si>
+  <si>
+    <t>Checked configs are used by this generator</t>
+  </si>
+  <si>
+    <t>Unassociate config from generator (uncheck)</t>
+  </si>
+  <si>
+    <t>1. Have a Generator with type = Time-Distributed
+2. At least one distribution config is CHECKED (associated)
+3. The Time Distribution tab is open</t>
+  </si>
+  <si>
+    <t>1. Find the "Distribution Configs" section
+2. Look at the list of configs
+3. Find a config that is currently CHECKED
+4. Click the checkbox to UNCHECK it
+5. Observe the changes</t>
+  </si>
+  <si>
+    <t>1. The checkbox becomes unchecked (empty)
+2. The config is no longer associated with this generator
+3. The Save button becomes blue/clickable
+4. After saving, this config will NOT be used by the generator</t>
+  </si>
+  <si>
+    <t>Unchecking removes association without deleting config</t>
+  </si>
+  <si>
+    <t>1. Have a Generator with type = Time-Distributed
+2. Multiple distribution configs exist (3 or more)
+3. The Time Distribution tab is open</t>
+  </si>
+  <si>
+    <t>1. Find the "Distribution Configs" section
+2. Check multiple config checkboxes (e.g., check 3 different configs)
+3. Save the changes
+4. Re-open the generator and check which configs are selected</t>
+  </si>
+  <si>
+    <t>1. Multiple checkboxes can be checked simultaneously
+2. All checked configs are associated with this generator
+3. After saving and reopening, all your selections persist
+4. The generator uses all associated configs for time distribution</t>
+  </si>
+  <si>
+    <t>Multiple configs can be associated with one generator</t>
+  </si>
+  <si>
+    <t>Add initial state modification</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected
+2. At least one State is defined in the model (e.g., "OrderStatus", "Priority")
+3. Click the Events tab (lightning/event icon)
+4. The State Modifications content is visible</t>
+  </si>
+  <si>
+    <t>1. Find the "Initial State Modifications" or "State Modifications" section
+2. Look for an "+ Add" button or dropdown to add a new modification
+3. Click to add a new state modification
+4. Select which state to modify (from dropdown of available states)
+5. Enter the initial value for that state (e.g., "New" or "High")</t>
+  </si>
+  <si>
+    <t>1. A new state modification appears in the list
+2. The modification shows:
+   - State name (e.g., "OrderStatus")
+   - Initial value (e.g., "New")
+3. Changes may AUTO-SAVE (check if Save button is needed)
+4. This value will be assigned to entities when they are generated</t>
+  </si>
+  <si>
+    <t>State modifications set initial values on generated entities</t>
+  </si>
+  <si>
+    <t>Edit existing state modification</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected
+2. At least one state modification already exists
+3. The Events tab is open</t>
+  </si>
+  <si>
+    <t>1. Find an existing state modification in the list
+2. Look for the value field or an Edit button
+3. Click to edit the modification
+4. Change the value (e.g., change "New" to "Pending")
+5. Click outside the field or confirm the change</t>
+  </si>
+  <si>
+    <t>1. The modification value updates to your new value
+2. The list shows the updated value
+3. Changes may AUTO-SAVE immediately
+4. After the change, generated entities will have this new initial state value</t>
+  </si>
+  <si>
+    <t>Modifying existing state initializations</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected
+2. At least one state modification exists
+3. The Events tab is open</t>
+  </si>
+  <si>
+    <t>1. Find an existing state modification in the list
+2. Look for a Delete button, trash icon, or remove option
+3. Click to delete/remove the modification
+4. Confirm deletion if prompted</t>
+  </si>
+  <si>
+    <t>1. The modification is removed from the list
+2. The modification no longer appears
+3. Changes may AUTO-SAVE immediately
+4. Generated entities will no longer have this state initialized</t>
+  </si>
+  <si>
+    <t>Removing state initialization</t>
+  </si>
+  <si>
+    <t>State modifications auto-save behavior</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected
+2. The Events tab is open</t>
+  </si>
+  <si>
+    <t>1. Make any change to state modifications:
+   - Add a new modification, OR
+   - Edit an existing value, OR
+   - Delete a modification
+2. Look at the bottom of the panel for Save/Cancel buttons
+3. Observe if changes save automatically</t>
+  </si>
+  <si>
+    <t>1. State modifications use AUTO-SAVE behavior:
+   - Changes are saved IMMEDIATELY without clicking Save
+   - The Save/Cancel buttons may be HIDDEN on this tab
+   - OR the Save button may flash briefly and become disabled
+2. You do NOT need to manually click Save
+3. Switching tabs or selecting another element preserves changes
+4. Document if this differs from expected behavior</t>
+  </si>
+  <si>
+    <t>Events tab typically uses auto-save</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected
+2. Click the States tab (usually the last tab icon)
+3. The States editor content is visible</t>
+  </si>
+  <si>
+    <t>1. Find the "+ Add" button or "Add State" option
+2. Click to add a new state
+3. A new state appears in the list (may have default name like "State1")
+4. Enter a name for the state (e.g., "OrderPriority")
+5. Configure any additional state properties if available</t>
+  </si>
+  <si>
+    <t>1. A new state appears in the list
+2. The state shows your entered name
+3. Changes AUTO-SAVE (no manual Save button needed)
+4. The state can now be used in state modifications and conditions
+5. NOTE: Save/Cancel buttons are typically HIDDEN on States tab</t>
+  </si>
+  <si>
+    <t>States tab uses auto-save - no Save button</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected
+2. At least one state exists in the list
+3. The States tab is open</t>
+  </si>
+  <si>
+    <t>1. Find an existing state in the list
+2. Click on the state name to edit it
+3. The name should become editable (text field or inline edit)
+4. Change the name (e.g., from "State1" to "CustomerType")
+5. Press Enter or click outside to confirm</t>
+  </si>
+  <si>
+    <t>1. The state name updates to your new value
+2. The list immediately reflects the change
+3. Changes AUTO-SAVE (no manual save needed)
+4. Anywhere this state was referenced will use the new name</t>
+  </si>
+  <si>
+    <t>Renaming states updates references</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected
+2. At least one state exists that is NOT currently in use
+3. The States tab is open</t>
+  </si>
+  <si>
+    <t>1. Find the state you want to delete
+2. Look for a Delete button, trash icon, or remove option
+3. Click to delete the state
+4. Confirm deletion if prompted</t>
+  </si>
+  <si>
+    <t>1. The state is removed from the list
+2. Changes AUTO-SAVE (no manual save needed)
+3. NOTE: You may not be able to delete a state that's currently in use
+4. Document any restrictions or error messages</t>
+  </si>
+  <si>
+    <t>May be restricted if state is referenced elsewhere</t>
+  </si>
+  <si>
+    <t>States tab hides Save/Cancel buttons</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected
+2. Go to any OTHER tab first (e.g., Basic Settings)
+3. Note the Save/Cancel buttons at the bottom</t>
+  </si>
+  <si>
+    <t>1. While on a tab with visible Save/Cancel buttons, note their position
+2. Now click the States tab
+3. Look at the bottom of the panel
+4. Check if Save/Cancel buttons are visible or hidden</t>
+  </si>
+  <si>
+    <t>1. On the States tab:
+   - Save and Cancel buttons are HIDDEN, OR
+   - They are visible but disabled/grayed
+2. This is because States uses AUTO-SAVE behavior
+3. Any changes to states save immediately
+4. You don't need to (and can't) manually save state changes</t>
+  </si>
+  <si>
+    <t>Auto-save means no manual Save needed</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Click on a Generator shape (oval/ellipse) to select it
+3. The Generator Editor panel appears on the right</t>
+  </si>
+  <si>
+    <t>1. DO NOT make any changes to the generator yet
+2. Look at the bottom of the Generator Editor panel
+3. Find the "Save" button
+4. Observe its state (enabled/disabled, blue/gray)</t>
+  </si>
+  <si>
+    <t>1. The Save button is DISABLED (grayed out, not clickable)
+2. This is because no changes have been made
+3. The Save button only becomes active when there are unsaved changes
+4. This is expected behavior for a "clean" form</t>
+  </si>
+  <si>
+    <t>Save disabled when no changes made</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected
+2. The Generator Editor panel is visible
+3. The Save button is currently disabled (gray)</t>
+  </si>
+  <si>
+    <t>1. Make ANY change to the generator:
+   - Change the name in Basic Settings, OR
+   - Change a value in Frequency Settings, OR
+   - Change the Generator Type
+2. Look at the Save button after making the change</t>
+  </si>
+  <si>
+    <t>1. The Save button changes from DISABLED (gray) to ENABLED (blue)
+2. The button is now clickable
+3. A Cancel button also appears (if not already visible)
+4. This indicates unsaved changes exist</t>
+  </si>
+  <si>
+    <t>Any change enables Save button</t>
+  </si>
+  <si>
+    <t>Save persists changes and disables button</t>
+  </si>
+  <si>
+    <t>1. Have a Generator with UNSAVED changes
+2. The Save button is currently blue/enabled
+3. You've modified something (name, type, values, etc.)</t>
+  </si>
+  <si>
+    <t>1. Click the Save button
+2. Wait for the save operation to complete
+3. Observe the Save button and the panel</t>
+  </si>
+  <si>
+    <t>1. The changes are saved to the model
+2. The Save button becomes DISABLED (gray) again
+3. The form returns to a "clean" state
+4. If you re-select the generator, your changes are still there
+5. A "Saving..." indicator may briefly appear</t>
+  </si>
+  <si>
+    <t>Save commits changes and resets dirty state</t>
+  </si>
+  <si>
+    <t>Cancel discards changes and resets form</t>
+  </si>
+  <si>
+    <t>1. Have a Generator with UNSAVED changes
+2. The Save button is currently blue/enabled
+3. You remember what the original values were</t>
+  </si>
+  <si>
+    <t>1. Click the Cancel button (next to Save)
+2. Observe the form fields
+3. Check that your changes are gone</t>
+  </si>
+  <si>
+    <t>1. All fields revert to their ORIGINAL values (before you made changes)
+2. Your modifications are discarded/lost
+3. The Save button becomes DISABLED (gray)
+4. The form is back to its "clean" state
+5. IMPORTANT: You cannot undo a Cancel</t>
+  </si>
+  <si>
+    <t>Cancel discards ALL unsaved changes</t>
+  </si>
+  <si>
+    <t>Cancel when no changes (after save)</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected
+2. You just saved changes (or no changes have been made)
+3. The form is in a "clean" state</t>
+  </si>
+  <si>
+    <t>1. Without making any new changes, click the Cancel button
+2. Observe what happens</t>
+  </si>
+  <si>
+    <t>1. Nothing bad happens - no crash or error
+2. The form remains unchanged
+3. The Cancel button may be:
+   - Disabled/hidden when no changes exist, OR
+   - Clicking it simply does nothing (no-op)
+4. This is safe behavior</t>
+  </si>
+  <si>
+    <t>Cancel with no changes is safe</t>
+  </si>
+  <si>
+    <t>Dirty state preserved when switching tabs</t>
+  </si>
+  <si>
+    <t>1. Have a Generator with UNSAVED changes
+2. The Save button is blue/enabled
+3. You changed something in Basic Settings, for example</t>
+  </si>
+  <si>
+    <t>1. While having unsaved changes, click a DIFFERENT tab:
+   - Go from Basic Settings to Frequency Settings, OR
+   - Go to another valid tab
+2. Then switch back to the original tab
+3. Check if your changes are still there</t>
+  </si>
+  <si>
+    <t>1. Your unsaved changes are PRESERVED when switching tabs
+2. The changed values still show in the form
+3. The Save button remains blue/enabled
+4. Changes are NOT lost by switching tabs within the same generator
+5. NOTE: States and Events tabs may behave differently (auto-save)</t>
+  </si>
+  <si>
+    <t>Tab switching doesn't discard changes</t>
+  </si>
+  <si>
+    <t>Save/Cancel buttons hidden on States tab</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected
+2. Go to any tab that shows Save/Cancel buttons (e.g., Basic Settings)
+3. Note the buttons at the bottom</t>
+  </si>
+  <si>
+    <t>1. While on a tab with visible Save/Cancel buttons, note their position
+2. Click the States tab
+3. Look at the bottom of the panel
+4. Check if Save/Cancel buttons are visible</t>
+  </si>
+  <si>
+    <t>1. On the States tab:
+   - Save and Cancel buttons are HIDDEN, OR
+   - They are visible but disabled
+2. This is because the States tab uses AUTO-SAVE
+3. Changes on States tab save immediately
+4. This is different from Basic/Frequency tabs</t>
+  </si>
+  <si>
+    <t>States tab has different save behavior</t>
+  </si>
+  <si>
+    <t>Switch to different generator loads new data</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The model has at least 2 Generator shapes with DIFFERENT names/settings
+3. Currently viewing Generator A in the Generator Editor</t>
+  </si>
+  <si>
+    <t>1. Note the current generator's name and settings (Generator A)
+2. In the LucidChart diagram, click on a DIFFERENT Generator shape (Generator B)
+3. Observe the Generator Editor panel
+4. Compare the displayed data to what you expect for Generator B</t>
+  </si>
+  <si>
+    <t>1. The Generator Editor panel updates to show Generator B's data
+2. The Generator Name field shows Generator B's name (not Generator A's)
+3. All other fields (type, frequency settings, etc.) show Generator B's values
+4. The panel completely refreshes with the new generator's data
+5. The tab structure may change if generators have different types</t>
+  </si>
+  <si>
+    <t>Selecting different generator reloads entire form</t>
+  </si>
+  <si>
+    <t>Switching generator auto-discards unsaved changes</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document with at least 2 Generators
+2. Select Generator A and make some changes (but DON'T save)
+3. The Save button should be blue/enabled</t>
+  </si>
+  <si>
+    <t>1. Make a change to Generator A (e.g., change the name to "MODIFIED")
+2. Do NOT click Save - leave the changes unsaved
+3. In the diagram, click on Generator B to select it
+4. Now click back on Generator A
+5. Check what name is shown for Generator A</t>
+  </si>
+  <si>
+    <t>1. When you switch to Generator B, Generator A's unsaved changes are AUTO-DISCARDED
+2. There may or may NOT be a warning prompt (test both scenarios)
+3. When you return to Generator A, it shows its ORIGINAL data
+4. Your unsaved changes ("MODIFIED") are LOST
+5. This is expected behavior - switching generators does not auto-save</t>
+  </si>
+  <si>
+    <t>IMPORTANT: Unsaved changes lost when switching</t>
+  </si>
+  <si>
+    <t>External update syncs to form (collaborative)</t>
+  </si>
+  <si>
+    <t>1. Have the same LucidChart document open in TWO browser windows/tabs
+2. Select the same Generator in both windows
+3. This tests collaborative editing sync</t>
+  </si>
+  <si>
+    <t>1. In Window 1: Select Generator A and view its name
+2. In Window 2: Select the SAME Generator A
+3. In Window 2: Change the name to "Changed by Window 2" and click Save
+4. In Window 1: Observe if/when the change appears
+5. You may need to click elsewhere then back, or wait for auto-sync</t>
+  </si>
+  <si>
+    <t>1. Window 1 eventually shows the updated name "Changed by Window 2"
+2. The sync may happen:
+   - Automatically after a short delay, OR
+   - When you re-select the generator, OR
+   - When the panel refreshes
+3. This tests that external changes are reflected in the UI
+4. Document the actual sync behavior observed</t>
+  </si>
+  <si>
+    <t>Tests collaborative real-time updates</t>
+  </si>
+  <si>
+    <t>Generator without exit connector shows ERROR</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document with a Quodsi model
+2. Create or find a Generator that has NO outgoing connector
+   - No arrow going FROM the generator TO another shape
+   - The generator is "dead end" - entities have nowhere to go</t>
+  </si>
+  <si>
+    <t>1. Click on the generator with no outgoing connector
+2. Open the Validation panel/tab (may be in left panel or separate tab)
+3. Look for validation errors related to this generator</t>
+  </si>
+  <si>
+    <t>1. A validation ERROR appears (red indicator)
+2. The error message says something like:
+   - "Generator has no exit connector" OR
+   - "Missing outgoing connection" OR
+   - "No destination for generated entities"
+3. This is an ERROR because generated entities have nowhere to go</t>
+  </si>
+  <si>
+    <t>Generators must have a path for entities to flow</t>
+  </si>
+  <si>
+    <t>Generator with multiple exit connectors shows WARNING</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document with a Quodsi model
+2. Create a Generator connected to 2 or more Activities
+   - Draw arrows from generator to Activity A AND Activity B</t>
+  </si>
+  <si>
+    <t>1. Click on the generator with multiple outgoing connectors
+2. Open the Validation panel/tab
+3. Look for validation warnings related to this generator</t>
+  </si>
+  <si>
+    <t>1. A validation WARNING may appear (yellow indicator)
+2. The warning might say something like:
+   - "Multiple exit connectors" OR
+   - "Generator sends to multiple destinations"
+3. This is a WARNING (not error) because it may be intentional
+4. Document if this warning actually appears or not</t>
+  </si>
+  <si>
+    <t>Multiple exits may be intentional but worth flagging</t>
+  </si>
+  <si>
+    <t>Missing entity reference shows ERROR</t>
+  </si>
+  <si>
+    <t>1. Have a Generator that references an Entity type
+2. DELETE that Entity type from the model
+3. The generator now references a non-existent entity</t>
+  </si>
+  <si>
+    <t>1. After deleting the entity, click on the generator
+2. Open the Validation panel/tab
+3. Look for validation errors related to missing entity</t>
+  </si>
+  <si>
+    <t>1. A validation ERROR appears (red indicator)
+2. The error message says something like:
+   - "Missing entity reference" OR
+   - "Referenced entity not found" OR
+   - "Invalid entity selection"
+3. This is an ERROR because the generator can't create entities of an unknown type</t>
+  </si>
+  <si>
+    <t>Generator's entity must exist in model</t>
+  </si>
+  <si>
+    <t>Invalid periodic occurrences shows ERROR</t>
+  </si>
+  <si>
+    <t>1. Have a Generator with type = Frequency-Based
+2. Navigate to Frequency Settings</t>
+  </si>
+  <si>
+    <t>1. Set Periodic Occurrences to an invalid value:
+   - Try a negative number (-1), OR
+   - Try a very large invalid number
+2. Save the changes
+3. Open the Validation panel/tab
+4. Look for validation errors</t>
+  </si>
+  <si>
+    <t>1. A validation ERROR appears if the value is truly invalid
+2. The error message indicates invalid periodic occurrences
+3. OR: The form may prevent saving invalid values entirely
+4. Document which behavior occurs</t>
+  </si>
+  <si>
+    <t>Negative or extreme values should be caught</t>
+  </si>
+  <si>
+    <t>Missing generator name shows WARNING</t>
+  </si>
+  <si>
+    <t>1. Have a Generator selected
+2. Go to Basic Settings tab</t>
+  </si>
+  <si>
+    <t>1. Clear the Generator Name field completely (make it empty)
+2. Try to Save
+3. If save succeeds, open the Validation panel/tab
+4. Look for validation messages about the name</t>
+  </si>
+  <si>
+    <t>1. EITHER: Form prevents saving with empty name (error on field)
+2. OR: Validation shows WARNING:
+   - "Missing name" OR
+   - "Generator name is blank"
+3. Empty names make the model confusing
+4. Document whether it's blocked or just warned</t>
+  </si>
+  <si>
+    <t>Names help identify elements in simulation results</t>
+  </si>
+  <si>
+    <t>Missing generationConfig shows ERROR</t>
+  </si>
+  <si>
+    <t>1. This tests a corrupt data scenario
+2. A generator exists with missing internal configuration
+3. You may need developer assistance to create this condition</t>
+  </si>
+  <si>
+    <t>1. If you have a generator with missing generationConfig (corrupt data):
+2. Open the Validation panel/tab
+3. Look for errors about missing configuration</t>
+  </si>
+  <si>
+    <t>1. A validation ERROR appears (red indicator)
+2. The error message says something like:
+   - "Missing generationConfig" OR
+   - "Generator configuration is incomplete"
+3. This is an ERROR because the generator cannot function
+4. This is typically a data corruption issue</t>
+  </si>
+  <si>
+    <t>Tests error handling for corrupt data</t>
+  </si>
+  <si>
+    <t>Invalid entities per creation shows ERROR</t>
+  </si>
+  <si>
+    <t>1. Find the "Entities Per Creation" field
+2. Try setting it to an invalid value:
+   - Set to 0 (zero), OR
+   - Set to a number greater than 1000
+3. Save and check validation</t>
+  </si>
+  <si>
+    <t>1. A validation ERROR appears (red indicator)
+2. The error message says something like:
+   - "Entities per creation must be between 1 and 1000" OR
+   - "Invalid entities per creation value"
+3. Valid range is typically 1-1000
+4. Document the actual allowed range</t>
+  </si>
+  <si>
+    <t>Entities per creation has min/max limits</t>
+  </si>
+  <si>
+    <t>Invalid max entities shows ERROR</t>
+  </si>
+  <si>
+    <t>1. Find the "Max Entities" field
+2. Try setting it to an invalid value:
+   - Set to 0 (unless that means unlimited), OR
+   - Set to a negative number
+3. Save and check validation</t>
+  </si>
+  <si>
+    <t>1. A validation ERROR may appear if the value is invalid
+2. The error message indicates invalid max entities
+3. Valid values are typically: positive numbers or Infinity/unlimited
+4. Document what values are accepted vs rejected</t>
+  </si>
+  <si>
+    <t>Max entities has constraints</t>
+  </si>
+  <si>
+    <t>Missing period interval duration shows ERROR</t>
+  </si>
+  <si>
+    <t>1. Have a Generator with type = Frequency-Based
+2. The Time Between Arrivals section has duration configuration</t>
+  </si>
+  <si>
+    <t>1. If possible, clear or corrupt the duration configuration
+2. This tests missing internal duration data
+3. Check the Validation panel</t>
+  </si>
+  <si>
+    <t>1. A validation ERROR appears if duration is missing
+2. The error message says something like:
+   - "Must have valid duration with distribution" OR
+   - "Period interval duration is required"
+3. Generators need a defined time between arrivals</t>
+  </si>
+  <si>
+    <t>Duration configuration is required</t>
+  </si>
+  <si>
+    <t>Negative period interval duration shows ERROR</t>
+  </si>
+  <si>
+    <t>1. Find the Time Between Arrivals value field
+2. Try setting the duration to -1 (negative)
+3. Save and check validation</t>
+  </si>
+  <si>
+    <t>1. A validation ERROR appears (red indicator)
+2. The error message says something like:
+   - "Duration value must be non-negative" OR
+   - "Invalid duration value"
+3. Time values cannot be negative</t>
+  </si>
+  <si>
+    <t>Duration must be &gt;= 0</t>
+  </si>
+  <si>
+    <t>Negative start delay shows ERROR</t>
+  </si>
+  <si>
+    <t>1. Find the "Start Delay" field
+2. Try setting it to -1 (negative one)
+3. Save and check validation</t>
+  </si>
+  <si>
+    <t>1. A validation ERROR appears (red indicator)
+2. The error message says something like:
+   - "Duration value must be non-negative" OR
+   - "Start delay cannot be negative"
+3. Start delay must be 0 or positive</t>
+  </si>
+  <si>
+    <t>Start delay must be &gt;= 0</t>
+  </si>
+  <si>
+    <t>Start delay exceeds interval shows WARNING</t>
+  </si>
+  <si>
+    <t>1. Set Time Between Arrivals to a small value (e.g., 5 minutes)
+2. Set Start Delay to a LARGER value (e.g., 60 minutes)
+3. Save and check validation</t>
+  </si>
+  <si>
+    <t>1. A validation WARNING may appear (yellow indicator)
+2. The warning might say something like:
+   - "Start delay longer than interval" OR
+   - "Start delay exceeds period interval"
+3. This is unusual but may be intentional
+4. Document if this warning actually appears</t>
+  </si>
+  <si>
+    <t>Flags potentially misconfigured timing</t>
+  </si>
+  <si>
+    <t>May exceed max entities shows WARNING</t>
+  </si>
+  <si>
+    <t>1. Have a Generator with type = Frequency-Based
+2. Set finite values for occurrences and entities per creation</t>
+  </si>
+  <si>
+    <t>1. Configure the generator so:
+   - periodicOccurrences × entitiesPerCreation &gt; maxEntities
+   - Example: 100 occurrences × 20 entities = 2000, but maxEntities = 500
+2. Save and check validation</t>
+  </si>
+  <si>
+    <t>1. A validation WARNING may appear (yellow indicator)
+2. The warning might say something like:
+   - "May reach maximum entities limit" OR
+   - "Configuration would exceed max entities"
+3. This warns that the generator will be capped early
+4. Document if this warning appears</t>
+  </si>
+  <si>
+    <t>Warns about potential entity cap</t>
+  </si>
+  <si>
+    <t>Overlapping generator start times shows WARNING</t>
+  </si>
+  <si>
+    <t>1. Have a model with 2 or more Generators
+2. Both generators have the same start delay value</t>
+  </si>
+  <si>
+    <t>1. Configure two generators to have the SAME start delay (e.g., both start at time 0)
+2. Save both generators
+3. Open the Validation panel
+4. Look for warnings about overlapping start times</t>
+  </si>
+  <si>
+    <t>1. A validation WARNING may appear (yellow indicator)
+2. The warning might say something like:
+   - "Multiple generators start at same time" OR
+   - "Overlapping generator start times"
+3. This could cause simulation spikes
+4. NOTE: This warning was recently removed from the code, so it may NOT appear</t>
+  </si>
+  <si>
+    <t>May have been removed - document behavior</t>
+  </si>
+  <si>
+    <t>High entity generation rate shows WARNING</t>
+  </si>
+  <si>
+    <t>1. Have one or more Generators configured
+2. Configure for very high generation rate</t>
+  </si>
+  <si>
+    <t>1. Configure generators with very high combined rate:
+   - Very short time between arrivals (e.g., 0.001 seconds)
+   - High entities per creation
+   - Combined rate &gt; 1000 entities per second
+2. Check validation</t>
+  </si>
+  <si>
+    <t>1. A validation WARNING may appear (yellow indicator)
+2. The warning might say something like:
+   - "High entity generation rate detected" OR
+   - "Generation rate may cause performance issues"
+3. This is a performance warning
+4. Document if this warning appears</t>
+  </si>
+  <si>
+    <t>Warns about potential performance impact</t>
+  </si>
+  <si>
+    <t>Fix validation error clears the error</t>
+  </si>
+  <si>
+    <t>1. Have a Generator with a known validation ERROR
+2. For example: generator with no exit connector
+3. The validation panel shows the error</t>
+  </si>
+  <si>
+    <t>1. Note the validation error showing
+2. Fix the error:
+   - For "no exit connector": add a connector from generator to an activity
+   - For "invalid value": correct the value
+3. Save the changes
+4. Check the Validation panel again</t>
+  </si>
+  <si>
+    <t>1. After fixing and saving, the error DISAPPEARS from the validation list
+2. If that was the only error, the generator may show green/no indicator
+3. The validation list updates to reflect the current model state
+4. Other unrelated errors (if any) remain until fixed</t>
+  </si>
+  <si>
+    <t>Validation updates when issues are fixed</t>
+  </si>
+  <si>
+    <t>Multiple validation errors shown for same generator</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document with a model
+2. Create a Generator that has MULTIPLE problems</t>
+  </si>
+  <si>
+    <t>1. Create a problematic generator:
+   - Remove its outgoing connector (no exit)
+   - Clear its name (empty name)
+   - Set invalid values in settings
+2. Save
+3. Open the Validation panel
+4. Count how many errors/warnings are shown for this generator</t>
+  </si>
+  <si>
+    <t>1. MULTIPLE validation errors/warnings appear for this single generator
+2. Each issue is listed separately:
+   - "No exit connector"
+   - "Missing name"
+   - "Invalid [setting]"
+3. The validation system shows ALL problems, not just the first
+4. This helps fix all issues at once</t>
+  </si>
+  <si>
+    <t>All validation issues should be visible</t>
+  </si>
+  <si>
+    <t>Click validation error navigates to element</t>
+  </si>
+  <si>
+    <t>1. Have a model with at least one validation error on a Generator
+2. You're NOT currently viewing that Generator
+3. The Validation panel is accessible</t>
+  </si>
+  <si>
+    <t>1. Open the Validation panel/tab
+2. Find an error related to a Generator
+3. Click on the error item (click the error message or link)
+4. Observe what happens in the diagram and editor panel</t>
+  </si>
+  <si>
+    <t>1. Clicking the error navigates you to the problematic Generator:
+   - The Generator becomes selected in the diagram
+   - The Generator Editor panel opens showing that generator
+   - The diagram may pan/scroll to show the generator
+2. This helps quickly locate and fix validation issues
+3. Document if clicking does navigate or just shows info</t>
+  </si>
+  <si>
+    <t>Click-to-navigate speeds up fixing issues</t>
+  </si>
+  <si>
+    <t>Very Long Generator Name</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Test that entering a very long name (500+ characters) is handled gracefully without breaking the UI</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Click on any Generator shape (oval/ellipse) in the diagram
+3. The right panel shows 'Generator Editor'
+4. The 'Basic Settings' tab (gear icon, first tab) is selected</t>
+  </si>
+  <si>
+    <t>1. Find the 'Generator Name' text box near the top of the panel
+2. Click inside the text box to place your cursor
+3. Select all existing text (Ctrl+A or triple-click)
+4. Paste or type a very long name - at least 500 characters
+   Example: Copy this and repeat it several times: 'ThisIsAVeryLongGeneratorNameForTestingPurposesOnly'
+5. Press Tab or click outside the text box to confirm
+6. Observe how the text box and panel handle the long name</t>
+  </si>
+  <si>
+    <t>1. The text box should accept the long name without crashing
+2. The text may be truncated in the display, or the box may show a scrollbar
+3. The Save button (bottom right, blue) should become enabled
+4. The panel should remain responsive and not freeze
+5. If you save and re-select the generator, the full name should be preserved</t>
+  </si>
+  <si>
+    <t>Pass/Fail</t>
+  </si>
+  <si>
+    <t>Rapid Save Button Clicks</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Test that clicking Save multiple times rapidly doesn't cause errors or duplicate saves</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Click on any Generator shape (oval/ellipse) in the diagram
+3. The right panel shows 'Generator Editor'
+4. Make a change to enable the Save button (e.g., modify the name)</t>
+  </si>
+  <si>
+    <t>1. Find the Save button at the bottom right of the panel (blue button)
+2. Quickly click the Save button multiple times in rapid succession (5+ clicks within 1 second)
+3. Watch the button and any status indicators
+4. After clicking, wait a moment for any processing to complete
+5. Click somewhere else on the diagram, then click back on the same generator</t>
+  </si>
+  <si>
+    <t>1. The first click should initiate the save
+2. Subsequent rapid clicks should be ignored or queued safely
+3. No error messages should appear
+4. The panel should not freeze or become unresponsive
+5. Only one save operation should actually occur
+6. When you re-select the generator, your changes should be saved correctly (only once)</t>
+  </si>
+  <si>
+    <t>Very Large Numbers in Numeric Fields</t>
+  </si>
+  <si>
+    <t>Test that entering extremely large numbers (999999999) in numeric fields is handled appropriately</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Click on a Generator shape (oval/ellipse) that is set to 'Frequency-Based' type
+3. The right panel shows 'Generator Editor'
+4. Click the 'Frequency' tab (second tab, clock icon)</t>
+  </si>
+  <si>
+    <t>1. Find the 'Time Between Arrivals' numeric field
+2. Click inside the field and select all existing text
+3. Type a very large number: 999999999
+4. Press Tab or click outside the field
+5. Observe how the field handles the large number
+6. Try the same with 'Max Occurrences' field if visible
+7. Also try negative numbers like -100 to test validation</t>
+  </si>
+  <si>
+    <t>1. The field should either:
+   a. Accept the large number if it's within valid range, OR
+   b. Show a validation error/warning if the number is too large, OR
+   c. Automatically cap the number to a maximum allowed value
+2. The panel should not crash or freeze
+3. Negative numbers should be rejected or show an error (times cannot be negative)
+4. If saved with a valid large number, re-selecting the generator should show the saved value</t>
+  </si>
+  <si>
+    <t>Browser Refresh During Edit</t>
+  </si>
+  <si>
+    <t>Test that unsaved changes are handled appropriately when the browser is refreshed</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Click on any Generator shape (oval/ellipse) in the diagram
+3. The right panel shows 'Generator Editor'
+4. Note the current generator name for reference</t>
+  </si>
+  <si>
+    <t>1. Find the 'Generator Name' text box in the Basic Settings tab
+2. Click inside and change the name to something memorable (e.g., 'UNSAVED TEST NAME')
+3. DO NOT click the Save button - leave the change unsaved
+4. The Save button should be blue/enabled showing unsaved changes
+5. Press F5 or Ctrl+R to refresh the browser page
+6. Wait for LucidChart to reload completely
+7. Click on the same Generator shape again
+8. Check the generator name in the panel</t>
+  </si>
+  <si>
+    <t>1. When refreshing, LucidChart may show a warning about unsaved changes (browser-level)
+2. After refresh, clicking the generator should show the ORIGINAL name (not 'UNSAVED TEST NAME')
+3. The unsaved changes should be lost (this is expected behavior)
+4. The panel should load normally without errors
+5. This confirms that only saved changes persist across browser refreshes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
+      <color/>
     </font>
   </fonts>
   <fills count="2">
@@ -1117,8 +2803,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+      <alignment/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1422,68 +3111,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" width="12.44140625"/>
+    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
+    <col bestFit="true" customWidth="true" max="3" min="3" width="31.44140625"/>
+    <col bestFit="true" customWidth="true" max="4" min="4" width="32"/>
+    <col bestFit="true" customWidth="true" max="5" min="5" width="33.88671875"/>
+    <col bestFit="true" customWidth="true" max="6" min="6" width="38"/>
+    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
+    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
+    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
+    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
+    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
+    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
+    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1491,19 +3180,43 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>346</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>347</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>348</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>349</v>
+      </c>
+      <c r="G2" t="s">
+        <v>286</v>
+      </c>
+      <c r="H2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I2" t="s">
+        <v>286</v>
+      </c>
+      <c r="J2" t="s">
+        <v>286</v>
+      </c>
+      <c r="K2" t="s">
+        <v>286</v>
+      </c>
+      <c r="L2" t="s">
+        <v>286</v>
+      </c>
+      <c r="M2" t="s">
+        <v>286</v>
+      </c>
+      <c r="N2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -1511,19 +3224,43 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>350</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>351</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>352</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>353</v>
+      </c>
+      <c r="G3" t="s">
+        <v>286</v>
+      </c>
+      <c r="H3" t="s">
+        <v>286</v>
+      </c>
+      <c r="I3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J3" t="s">
+        <v>286</v>
+      </c>
+      <c r="K3" t="s">
+        <v>286</v>
+      </c>
+      <c r="L3" t="s">
+        <v>286</v>
+      </c>
+      <c r="M3" t="s">
+        <v>286</v>
+      </c>
+      <c r="N3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -1531,19 +3268,43 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>355</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>356</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>357</v>
       </c>
       <c r="F4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>358</v>
+      </c>
+      <c r="G4" t="s">
+        <v>286</v>
+      </c>
+      <c r="H4" t="s">
+        <v>286</v>
+      </c>
+      <c r="I4" t="s">
+        <v>286</v>
+      </c>
+      <c r="J4" t="s">
+        <v>286</v>
+      </c>
+      <c r="K4" t="s">
+        <v>286</v>
+      </c>
+      <c r="L4" t="s">
+        <v>286</v>
+      </c>
+      <c r="M4" t="s">
+        <v>286</v>
+      </c>
+      <c r="N4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -1551,19 +3312,43 @@
         <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>360</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>361</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>362</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+        <v>363</v>
+      </c>
+      <c r="G5" t="s">
+        <v>286</v>
+      </c>
+      <c r="H5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I5" t="s">
+        <v>286</v>
+      </c>
+      <c r="J5" t="s">
+        <v>286</v>
+      </c>
+      <c r="K5" t="s">
+        <v>286</v>
+      </c>
+      <c r="L5" t="s">
+        <v>286</v>
+      </c>
+      <c r="M5" t="s">
+        <v>286</v>
+      </c>
+      <c r="N5" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -1574,16 +3359,40 @@
         <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>365</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>366</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+        <v>367</v>
+      </c>
+      <c r="G6" t="s">
+        <v>286</v>
+      </c>
+      <c r="H6" t="s">
+        <v>286</v>
+      </c>
+      <c r="I6" t="s">
+        <v>286</v>
+      </c>
+      <c r="J6" t="s">
+        <v>286</v>
+      </c>
+      <c r="K6" t="s">
+        <v>286</v>
+      </c>
+      <c r="L6" t="s">
+        <v>286</v>
+      </c>
+      <c r="M6" t="s">
+        <v>286</v>
+      </c>
+      <c r="N6" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -1591,19 +3400,43 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>369</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>370</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>371</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+        <v>372</v>
+      </c>
+      <c r="G7" t="s">
+        <v>286</v>
+      </c>
+      <c r="H7" t="s">
+        <v>286</v>
+      </c>
+      <c r="I7" t="s">
+        <v>286</v>
+      </c>
+      <c r="J7" t="s">
+        <v>286</v>
+      </c>
+      <c r="K7" t="s">
+        <v>286</v>
+      </c>
+      <c r="L7" t="s">
+        <v>286</v>
+      </c>
+      <c r="M7" t="s">
+        <v>286</v>
+      </c>
+      <c r="N7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -1611,19 +3444,43 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>374</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>370</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>375</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+        <v>376</v>
+      </c>
+      <c r="G8" t="s">
+        <v>286</v>
+      </c>
+      <c r="H8" t="s">
+        <v>286</v>
+      </c>
+      <c r="I8" t="s">
+        <v>286</v>
+      </c>
+      <c r="J8" t="s">
+        <v>286</v>
+      </c>
+      <c r="K8" t="s">
+        <v>286</v>
+      </c>
+      <c r="L8" t="s">
+        <v>286</v>
+      </c>
+      <c r="M8" t="s">
+        <v>286</v>
+      </c>
+      <c r="N8" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -1631,16 +3488,40 @@
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>377</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>378</v>
       </c>
       <c r="E9" t="s">
-        <v>50</v>
+        <v>379</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>380</v>
+      </c>
+      <c r="G9" t="s">
+        <v>286</v>
+      </c>
+      <c r="H9" t="s">
+        <v>286</v>
+      </c>
+      <c r="I9" t="s">
+        <v>286</v>
+      </c>
+      <c r="J9" t="s">
+        <v>286</v>
+      </c>
+      <c r="K9" t="s">
+        <v>286</v>
+      </c>
+      <c r="L9" t="s">
+        <v>286</v>
+      </c>
+      <c r="M9" t="s">
+        <v>286</v>
+      </c>
+      <c r="N9" t="s">
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -1651,145 +3532,241 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" width="13.44140625"/>
+    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
+    <col bestFit="true" customWidth="true" max="3" min="3" width="23.33203125"/>
+    <col bestFit="true" customWidth="true" max="4" min="4" width="21.88671875"/>
+    <col bestFit="true" customWidth="true" max="5" min="5" width="28.88671875"/>
+    <col bestFit="true" customWidth="true" max="6" min="6" width="31.88671875"/>
+    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
+    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
+    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
+    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
+    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
+    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
+    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>264</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>653</v>
       </c>
       <c r="C2" t="s">
-        <v>265</v>
+        <v>654</v>
       </c>
       <c r="D2" t="s">
-        <v>266</v>
+        <v>655</v>
       </c>
       <c r="E2" t="s">
-        <v>267</v>
+        <v>656</v>
       </c>
       <c r="F2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>657</v>
+      </c>
+      <c r="G2" t="s">
+        <v>658</v>
+      </c>
+      <c r="H2" t="s">
+        <v>659</v>
+      </c>
+      <c r="I2" t="s">
+        <v>286</v>
+      </c>
+      <c r="J2" t="s">
+        <v>286</v>
+      </c>
+      <c r="K2" t="s">
+        <v>286</v>
+      </c>
+      <c r="L2" t="s">
+        <v>286</v>
+      </c>
+      <c r="M2" t="s">
+        <v>286</v>
+      </c>
+      <c r="N2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>269</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>660</v>
       </c>
       <c r="C3" t="s">
-        <v>270</v>
+        <v>661</v>
       </c>
       <c r="D3" t="s">
-        <v>213</v>
+        <v>662</v>
       </c>
       <c r="E3" t="s">
-        <v>271</v>
+        <v>663</v>
       </c>
       <c r="F3" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>664</v>
+      </c>
+      <c r="G3" t="s">
+        <v>665</v>
+      </c>
+      <c r="H3" t="s">
+        <v>659</v>
+      </c>
+      <c r="I3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J3" t="s">
+        <v>286</v>
+      </c>
+      <c r="K3" t="s">
+        <v>286</v>
+      </c>
+      <c r="L3" t="s">
+        <v>286</v>
+      </c>
+      <c r="M3" t="s">
+        <v>286</v>
+      </c>
+      <c r="N3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>273</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>666</v>
       </c>
       <c r="C4" t="s">
-        <v>274</v>
+        <v>661</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>667</v>
       </c>
       <c r="E4" t="s">
-        <v>275</v>
+        <v>668</v>
       </c>
       <c r="F4" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>669</v>
+      </c>
+      <c r="G4" t="s">
+        <v>670</v>
+      </c>
+      <c r="H4" t="s">
+        <v>659</v>
+      </c>
+      <c r="I4" t="s">
+        <v>286</v>
+      </c>
+      <c r="J4" t="s">
+        <v>286</v>
+      </c>
+      <c r="K4" t="s">
+        <v>286</v>
+      </c>
+      <c r="L4" t="s">
+        <v>286</v>
+      </c>
+      <c r="M4" t="s">
+        <v>286</v>
+      </c>
+      <c r="N4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>277</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>671</v>
       </c>
       <c r="C5" t="s">
-        <v>278</v>
+        <v>654</v>
       </c>
       <c r="D5" t="s">
-        <v>240</v>
+        <v>672</v>
       </c>
       <c r="E5" t="s">
-        <v>279</v>
+        <v>673</v>
       </c>
       <c r="F5" t="s">
-        <v>280</v>
+        <v>674</v>
+      </c>
+      <c r="G5" t="s">
+        <v>675</v>
+      </c>
+      <c r="H5" t="s">
+        <v>659</v>
+      </c>
+      <c r="I5" t="s">
+        <v>286</v>
+      </c>
+      <c r="J5" t="s">
+        <v>286</v>
+      </c>
+      <c r="K5" t="s">
+        <v>286</v>
+      </c>
+      <c r="L5" t="s">
+        <v>286</v>
+      </c>
+      <c r="M5" t="s">
+        <v>286</v>
+      </c>
+      <c r="N5" t="s">
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -1800,68 +3777,68 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" width="13.77734375"/>
+    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
+    <col bestFit="true" customWidth="true" max="3" min="3" width="23.44140625"/>
+    <col bestFit="true" customWidth="true" max="4" min="4" width="25.109375"/>
+    <col bestFit="true" customWidth="true" max="5" min="5" width="33.77734375"/>
+    <col bestFit="true" customWidth="true" max="6" min="6" width="35.6640625"/>
+    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
+    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
+    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
+    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
+    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
+    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
+    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -1872,16 +3849,40 @@
         <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>382</v>
       </c>
       <c r="E2" t="s">
-        <v>55</v>
+        <v>383</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>384</v>
+      </c>
+      <c r="G2" t="s">
+        <v>286</v>
+      </c>
+      <c r="H2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I2" t="s">
+        <v>286</v>
+      </c>
+      <c r="J2" t="s">
+        <v>286</v>
+      </c>
+      <c r="K2" t="s">
+        <v>286</v>
+      </c>
+      <c r="L2" t="s">
+        <v>286</v>
+      </c>
+      <c r="M2" t="s">
+        <v>286</v>
+      </c>
+      <c r="N2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>57</v>
       </c>
@@ -1892,16 +3893,40 @@
         <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>385</v>
       </c>
       <c r="E3" t="s">
-        <v>60</v>
+        <v>386</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>387</v>
+      </c>
+      <c r="G3" t="s">
+        <v>286</v>
+      </c>
+      <c r="H3" t="s">
+        <v>286</v>
+      </c>
+      <c r="I3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J3" t="s">
+        <v>286</v>
+      </c>
+      <c r="K3" t="s">
+        <v>286</v>
+      </c>
+      <c r="L3" t="s">
+        <v>286</v>
+      </c>
+      <c r="M3" t="s">
+        <v>286</v>
+      </c>
+      <c r="N3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -1912,16 +3937,40 @@
         <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>389</v>
       </c>
       <c r="E4" t="s">
-        <v>64</v>
+        <v>390</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>391</v>
+      </c>
+      <c r="G4" t="s">
+        <v>286</v>
+      </c>
+      <c r="H4" t="s">
+        <v>286</v>
+      </c>
+      <c r="I4" t="s">
+        <v>286</v>
+      </c>
+      <c r="J4" t="s">
+        <v>286</v>
+      </c>
+      <c r="K4" t="s">
+        <v>286</v>
+      </c>
+      <c r="L4" t="s">
+        <v>286</v>
+      </c>
+      <c r="M4" t="s">
+        <v>286</v>
+      </c>
+      <c r="N4" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>66</v>
       </c>
@@ -1932,16 +3981,40 @@
         <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>393</v>
       </c>
       <c r="E5" t="s">
-        <v>68</v>
+        <v>394</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+        <v>395</v>
+      </c>
+      <c r="G5" t="s">
+        <v>286</v>
+      </c>
+      <c r="H5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I5" t="s">
+        <v>286</v>
+      </c>
+      <c r="J5" t="s">
+        <v>286</v>
+      </c>
+      <c r="K5" t="s">
+        <v>286</v>
+      </c>
+      <c r="L5" t="s">
+        <v>286</v>
+      </c>
+      <c r="M5" t="s">
+        <v>286</v>
+      </c>
+      <c r="N5" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>70</v>
       </c>
@@ -1952,16 +4025,40 @@
         <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>397</v>
       </c>
       <c r="E6" t="s">
-        <v>72</v>
+        <v>398</v>
       </c>
       <c r="F6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+        <v>399</v>
+      </c>
+      <c r="G6" t="s">
+        <v>286</v>
+      </c>
+      <c r="H6" t="s">
+        <v>286</v>
+      </c>
+      <c r="I6" t="s">
+        <v>286</v>
+      </c>
+      <c r="J6" t="s">
+        <v>286</v>
+      </c>
+      <c r="K6" t="s">
+        <v>286</v>
+      </c>
+      <c r="L6" t="s">
+        <v>286</v>
+      </c>
+      <c r="M6" t="s">
+        <v>286</v>
+      </c>
+      <c r="N6" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>74</v>
       </c>
@@ -1969,16 +4066,40 @@
         <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>401</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>402</v>
       </c>
       <c r="E7" t="s">
-        <v>76</v>
+        <v>403</v>
       </c>
       <c r="F7" t="s">
-        <v>77</v>
+        <v>404</v>
+      </c>
+      <c r="G7" t="s">
+        <v>286</v>
+      </c>
+      <c r="H7" t="s">
+        <v>286</v>
+      </c>
+      <c r="I7" t="s">
+        <v>286</v>
+      </c>
+      <c r="J7" t="s">
+        <v>286</v>
+      </c>
+      <c r="K7" t="s">
+        <v>286</v>
+      </c>
+      <c r="L7" t="s">
+        <v>286</v>
+      </c>
+      <c r="M7" t="s">
+        <v>286</v>
+      </c>
+      <c r="N7" t="s">
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -1989,69 +4110,69 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" width="13.33203125"/>
+    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
+    <col bestFit="true" customWidth="true" max="3" min="3" width="30.5546875"/>
+    <col bestFit="true" customWidth="true" max="4" min="4" width="17.21875"/>
+    <col bestFit="true" customWidth="true" max="5" min="5" width="41.33203125"/>
+    <col bestFit="true" customWidth="true" max="6" min="6" width="28.109375"/>
+    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
+    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
+    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
+    <col bestFit="true" customWidth="true" max="10" min="10" width="8.88671875"/>
+    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
+    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
+    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
+    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>78</v>
       </c>
@@ -2062,16 +4183,40 @@
         <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>406</v>
       </c>
       <c r="E2" t="s">
-        <v>81</v>
+        <v>407</v>
       </c>
       <c r="F2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>408</v>
+      </c>
+      <c r="G2" t="s">
+        <v>286</v>
+      </c>
+      <c r="H2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I2" t="s">
+        <v>286</v>
+      </c>
+      <c r="J2" t="s">
+        <v>286</v>
+      </c>
+      <c r="K2" t="s">
+        <v>286</v>
+      </c>
+      <c r="L2" t="s">
+        <v>286</v>
+      </c>
+      <c r="M2" t="s">
+        <v>286</v>
+      </c>
+      <c r="N2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>83</v>
       </c>
@@ -2082,16 +4227,40 @@
         <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>410</v>
       </c>
       <c r="E3" t="s">
-        <v>85</v>
+        <v>411</v>
       </c>
       <c r="F3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>412</v>
+      </c>
+      <c r="G3" t="s">
+        <v>286</v>
+      </c>
+      <c r="H3" t="s">
+        <v>286</v>
+      </c>
+      <c r="I3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J3" t="s">
+        <v>286</v>
+      </c>
+      <c r="K3" t="s">
+        <v>286</v>
+      </c>
+      <c r="L3" t="s">
+        <v>286</v>
+      </c>
+      <c r="M3" t="s">
+        <v>286</v>
+      </c>
+      <c r="N3" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>87</v>
       </c>
@@ -2102,16 +4271,40 @@
         <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>410</v>
       </c>
       <c r="E4" t="s">
-        <v>89</v>
+        <v>414</v>
       </c>
       <c r="F4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>415</v>
+      </c>
+      <c r="G4" t="s">
+        <v>286</v>
+      </c>
+      <c r="H4" t="s">
+        <v>286</v>
+      </c>
+      <c r="I4" t="s">
+        <v>286</v>
+      </c>
+      <c r="J4" t="s">
+        <v>286</v>
+      </c>
+      <c r="K4" t="s">
+        <v>286</v>
+      </c>
+      <c r="L4" t="s">
+        <v>286</v>
+      </c>
+      <c r="M4" t="s">
+        <v>286</v>
+      </c>
+      <c r="N4" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>91</v>
       </c>
@@ -2122,16 +4315,40 @@
         <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>417</v>
       </c>
       <c r="E5" t="s">
-        <v>93</v>
+        <v>418</v>
       </c>
       <c r="F5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+        <v>419</v>
+      </c>
+      <c r="G5" t="s">
+        <v>286</v>
+      </c>
+      <c r="H5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I5" t="s">
+        <v>286</v>
+      </c>
+      <c r="J5" t="s">
+        <v>286</v>
+      </c>
+      <c r="K5" t="s">
+        <v>286</v>
+      </c>
+      <c r="L5" t="s">
+        <v>286</v>
+      </c>
+      <c r="M5" t="s">
+        <v>286</v>
+      </c>
+      <c r="N5" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>95</v>
       </c>
@@ -2139,19 +4356,43 @@
         <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>421</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>417</v>
       </c>
       <c r="E6" t="s">
-        <v>97</v>
+        <v>422</v>
       </c>
       <c r="F6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+        <v>423</v>
+      </c>
+      <c r="G6" t="s">
+        <v>286</v>
+      </c>
+      <c r="H6" t="s">
+        <v>286</v>
+      </c>
+      <c r="I6" t="s">
+        <v>286</v>
+      </c>
+      <c r="J6" t="s">
+        <v>286</v>
+      </c>
+      <c r="K6" t="s">
+        <v>286</v>
+      </c>
+      <c r="L6" t="s">
+        <v>286</v>
+      </c>
+      <c r="M6" t="s">
+        <v>286</v>
+      </c>
+      <c r="N6" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>99</v>
       </c>
@@ -2162,16 +4403,40 @@
         <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>417</v>
       </c>
       <c r="E7" t="s">
-        <v>101</v>
+        <v>425</v>
       </c>
       <c r="F7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+        <v>426</v>
+      </c>
+      <c r="G7" t="s">
+        <v>286</v>
+      </c>
+      <c r="H7" t="s">
+        <v>286</v>
+      </c>
+      <c r="I7" t="s">
+        <v>286</v>
+      </c>
+      <c r="J7" t="s">
+        <v>286</v>
+      </c>
+      <c r="K7" t="s">
+        <v>286</v>
+      </c>
+      <c r="L7" t="s">
+        <v>286</v>
+      </c>
+      <c r="M7" t="s">
+        <v>286</v>
+      </c>
+      <c r="N7" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>103</v>
       </c>
@@ -2182,16 +4447,40 @@
         <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>417</v>
       </c>
       <c r="E8" t="s">
-        <v>105</v>
+        <v>428</v>
       </c>
       <c r="F8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+        <v>429</v>
+      </c>
+      <c r="G8" t="s">
+        <v>286</v>
+      </c>
+      <c r="H8" t="s">
+        <v>286</v>
+      </c>
+      <c r="I8" t="s">
+        <v>286</v>
+      </c>
+      <c r="J8" t="s">
+        <v>286</v>
+      </c>
+      <c r="K8" t="s">
+        <v>286</v>
+      </c>
+      <c r="L8" t="s">
+        <v>286</v>
+      </c>
+      <c r="M8" t="s">
+        <v>286</v>
+      </c>
+      <c r="N8" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
         <v>106</v>
       </c>
@@ -2202,16 +4491,40 @@
         <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>417</v>
       </c>
       <c r="E9" t="s">
-        <v>108</v>
+        <v>431</v>
       </c>
       <c r="F9" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+        <v>432</v>
+      </c>
+      <c r="G9" t="s">
+        <v>286</v>
+      </c>
+      <c r="H9" t="s">
+        <v>286</v>
+      </c>
+      <c r="I9" t="s">
+        <v>286</v>
+      </c>
+      <c r="J9" t="s">
+        <v>286</v>
+      </c>
+      <c r="K9" t="s">
+        <v>286</v>
+      </c>
+      <c r="L9" t="s">
+        <v>286</v>
+      </c>
+      <c r="M9" t="s">
+        <v>286</v>
+      </c>
+      <c r="N9" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
         <v>110</v>
       </c>
@@ -2222,16 +4535,40 @@
         <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>417</v>
       </c>
       <c r="E10" t="s">
-        <v>112</v>
+        <v>434</v>
       </c>
       <c r="F10" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+        <v>435</v>
+      </c>
+      <c r="G10" t="s">
+        <v>286</v>
+      </c>
+      <c r="H10" t="s">
+        <v>286</v>
+      </c>
+      <c r="I10" t="s">
+        <v>286</v>
+      </c>
+      <c r="J10" t="s">
+        <v>286</v>
+      </c>
+      <c r="K10" t="s">
+        <v>286</v>
+      </c>
+      <c r="L10" t="s">
+        <v>286</v>
+      </c>
+      <c r="M10" t="s">
+        <v>286</v>
+      </c>
+      <c r="N10" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
         <v>114</v>
       </c>
@@ -2242,13 +4579,37 @@
         <v>115</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>417</v>
       </c>
       <c r="E11" t="s">
-        <v>116</v>
+        <v>437</v>
       </c>
       <c r="F11" t="s">
-        <v>117</v>
+        <v>438</v>
+      </c>
+      <c r="G11" t="s">
+        <v>286</v>
+      </c>
+      <c r="H11" t="s">
+        <v>286</v>
+      </c>
+      <c r="I11" t="s">
+        <v>286</v>
+      </c>
+      <c r="J11" t="s">
+        <v>286</v>
+      </c>
+      <c r="K11" t="s">
+        <v>286</v>
+      </c>
+      <c r="L11" t="s">
+        <v>286</v>
+      </c>
+      <c r="M11" t="s">
+        <v>286</v>
+      </c>
+      <c r="N11" t="s">
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -2259,68 +4620,68 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" width="12.5546875"/>
+    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
+    <col bestFit="true" customWidth="true" max="3" min="3" width="27.109375"/>
+    <col bestFit="true" customWidth="true" max="4" min="4" width="35.88671875"/>
+    <col bestFit="true" customWidth="true" max="5" min="5" width="31.88671875"/>
+    <col bestFit="true" customWidth="true" max="6" min="6" width="34.21875"/>
+    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
+    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
+    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
+    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
+    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
+    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
+    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>118</v>
       </c>
@@ -2328,19 +4689,43 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>119</v>
+        <v>440</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>441</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>442</v>
       </c>
       <c r="F2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+      <c r="G2" t="s">
+        <v>286</v>
+      </c>
+      <c r="H2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I2" t="s">
+        <v>286</v>
+      </c>
+      <c r="J2" t="s">
+        <v>286</v>
+      </c>
+      <c r="K2" t="s">
+        <v>286</v>
+      </c>
+      <c r="L2" t="s">
+        <v>286</v>
+      </c>
+      <c r="M2" t="s">
+        <v>286</v>
+      </c>
+      <c r="N2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>123</v>
       </c>
@@ -2348,19 +4733,43 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>124</v>
+        <v>445</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>446</v>
       </c>
       <c r="E3" t="s">
-        <v>126</v>
+        <v>447</v>
       </c>
       <c r="F3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>448</v>
+      </c>
+      <c r="G3" t="s">
+        <v>286</v>
+      </c>
+      <c r="H3" t="s">
+        <v>286</v>
+      </c>
+      <c r="I3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J3" t="s">
+        <v>286</v>
+      </c>
+      <c r="K3" t="s">
+        <v>286</v>
+      </c>
+      <c r="L3" t="s">
+        <v>286</v>
+      </c>
+      <c r="M3" t="s">
+        <v>286</v>
+      </c>
+      <c r="N3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>128</v>
       </c>
@@ -2371,16 +4780,40 @@
         <v>129</v>
       </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>449</v>
       </c>
       <c r="E4" t="s">
-        <v>130</v>
+        <v>450</v>
       </c>
       <c r="F4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>451</v>
+      </c>
+      <c r="G4" t="s">
+        <v>286</v>
+      </c>
+      <c r="H4" t="s">
+        <v>286</v>
+      </c>
+      <c r="I4" t="s">
+        <v>286</v>
+      </c>
+      <c r="J4" t="s">
+        <v>286</v>
+      </c>
+      <c r="K4" t="s">
+        <v>286</v>
+      </c>
+      <c r="L4" t="s">
+        <v>286</v>
+      </c>
+      <c r="M4" t="s">
+        <v>286</v>
+      </c>
+      <c r="N4" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>132</v>
       </c>
@@ -2388,19 +4821,43 @@
         <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>133</v>
+        <v>453</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>449</v>
       </c>
       <c r="E5" t="s">
-        <v>134</v>
+        <v>454</v>
       </c>
       <c r="F5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+        <v>455</v>
+      </c>
+      <c r="G5" t="s">
+        <v>286</v>
+      </c>
+      <c r="H5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I5" t="s">
+        <v>286</v>
+      </c>
+      <c r="J5" t="s">
+        <v>286</v>
+      </c>
+      <c r="K5" t="s">
+        <v>286</v>
+      </c>
+      <c r="L5" t="s">
+        <v>286</v>
+      </c>
+      <c r="M5" t="s">
+        <v>286</v>
+      </c>
+      <c r="N5" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>136</v>
       </c>
@@ -2408,19 +4865,43 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>137</v>
+        <v>457</v>
       </c>
       <c r="D6" t="s">
-        <v>138</v>
+        <v>458</v>
       </c>
       <c r="E6" t="s">
-        <v>139</v>
+        <v>459</v>
       </c>
       <c r="F6" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+        <v>460</v>
+      </c>
+      <c r="G6" t="s">
+        <v>286</v>
+      </c>
+      <c r="H6" t="s">
+        <v>286</v>
+      </c>
+      <c r="I6" t="s">
+        <v>286</v>
+      </c>
+      <c r="J6" t="s">
+        <v>286</v>
+      </c>
+      <c r="K6" t="s">
+        <v>286</v>
+      </c>
+      <c r="L6" t="s">
+        <v>286</v>
+      </c>
+      <c r="M6" t="s">
+        <v>286</v>
+      </c>
+      <c r="N6" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>141</v>
       </c>
@@ -2428,19 +4909,43 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>142</v>
+        <v>462</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>463</v>
       </c>
       <c r="E7" t="s">
-        <v>144</v>
+        <v>464</v>
       </c>
       <c r="F7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+        <v>465</v>
+      </c>
+      <c r="G7" t="s">
+        <v>286</v>
+      </c>
+      <c r="H7" t="s">
+        <v>286</v>
+      </c>
+      <c r="I7" t="s">
+        <v>286</v>
+      </c>
+      <c r="J7" t="s">
+        <v>286</v>
+      </c>
+      <c r="K7" t="s">
+        <v>286</v>
+      </c>
+      <c r="L7" t="s">
+        <v>286</v>
+      </c>
+      <c r="M7" t="s">
+        <v>286</v>
+      </c>
+      <c r="N7" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>146</v>
       </c>
@@ -2451,16 +4956,40 @@
         <v>147</v>
       </c>
       <c r="D8" t="s">
-        <v>143</v>
+        <v>466</v>
       </c>
       <c r="E8" t="s">
-        <v>148</v>
+        <v>467</v>
       </c>
       <c r="F8" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+        <v>468</v>
+      </c>
+      <c r="G8" t="s">
+        <v>286</v>
+      </c>
+      <c r="H8" t="s">
+        <v>286</v>
+      </c>
+      <c r="I8" t="s">
+        <v>286</v>
+      </c>
+      <c r="J8" t="s">
+        <v>286</v>
+      </c>
+      <c r="K8" t="s">
+        <v>286</v>
+      </c>
+      <c r="L8" t="s">
+        <v>286</v>
+      </c>
+      <c r="M8" t="s">
+        <v>286</v>
+      </c>
+      <c r="N8" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
         <v>150</v>
       </c>
@@ -2468,19 +4997,43 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>151</v>
+        <v>470</v>
       </c>
       <c r="D9" t="s">
-        <v>152</v>
+        <v>471</v>
       </c>
       <c r="E9" t="s">
-        <v>153</v>
+        <v>472</v>
       </c>
       <c r="F9" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+        <v>473</v>
+      </c>
+      <c r="G9" t="s">
+        <v>286</v>
+      </c>
+      <c r="H9" t="s">
+        <v>286</v>
+      </c>
+      <c r="I9" t="s">
+        <v>286</v>
+      </c>
+      <c r="J9" t="s">
+        <v>286</v>
+      </c>
+      <c r="K9" t="s">
+        <v>286</v>
+      </c>
+      <c r="L9" t="s">
+        <v>286</v>
+      </c>
+      <c r="M9" t="s">
+        <v>286</v>
+      </c>
+      <c r="N9" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
         <v>155</v>
       </c>
@@ -2488,19 +5041,43 @@
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>156</v>
+        <v>475</v>
       </c>
       <c r="D10" t="s">
-        <v>157</v>
+        <v>476</v>
       </c>
       <c r="E10" t="s">
-        <v>158</v>
+        <v>477</v>
       </c>
       <c r="F10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+        <v>478</v>
+      </c>
+      <c r="G10" t="s">
+        <v>286</v>
+      </c>
+      <c r="H10" t="s">
+        <v>286</v>
+      </c>
+      <c r="I10" t="s">
+        <v>286</v>
+      </c>
+      <c r="J10" t="s">
+        <v>286</v>
+      </c>
+      <c r="K10" t="s">
+        <v>286</v>
+      </c>
+      <c r="L10" t="s">
+        <v>286</v>
+      </c>
+      <c r="M10" t="s">
+        <v>286</v>
+      </c>
+      <c r="N10" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
         <v>160</v>
       </c>
@@ -2511,13 +5088,37 @@
         <v>161</v>
       </c>
       <c r="D11" t="s">
-        <v>162</v>
+        <v>480</v>
       </c>
       <c r="E11" t="s">
-        <v>163</v>
+        <v>481</v>
       </c>
       <c r="F11" t="s">
-        <v>164</v>
+        <v>482</v>
+      </c>
+      <c r="G11" t="s">
+        <v>286</v>
+      </c>
+      <c r="H11" t="s">
+        <v>286</v>
+      </c>
+      <c r="I11" t="s">
+        <v>286</v>
+      </c>
+      <c r="J11" t="s">
+        <v>286</v>
+      </c>
+      <c r="K11" t="s">
+        <v>286</v>
+      </c>
+      <c r="L11" t="s">
+        <v>286</v>
+      </c>
+      <c r="M11" t="s">
+        <v>286</v>
+      </c>
+      <c r="N11" t="s">
+        <v>483</v>
       </c>
     </row>
   </sheetData>
@@ -2528,68 +5129,68 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" width="14.44140625"/>
+    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
+    <col bestFit="true" customWidth="true" max="3" min="3" width="25.77734375"/>
+    <col bestFit="true" customWidth="true" max="4" min="4" width="22.109375"/>
+    <col bestFit="true" customWidth="true" max="5" min="5" width="31.88671875"/>
+    <col bestFit="true" customWidth="true" max="6" min="6" width="36.88671875"/>
+    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
+    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
+    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
+    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
+    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
+    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
+    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>165</v>
       </c>
@@ -2597,19 +5198,43 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>166</v>
+        <v>484</v>
       </c>
       <c r="D2" t="s">
-        <v>167</v>
+        <v>485</v>
       </c>
       <c r="E2" t="s">
-        <v>168</v>
+        <v>486</v>
       </c>
       <c r="F2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>487</v>
+      </c>
+      <c r="G2" t="s">
+        <v>286</v>
+      </c>
+      <c r="H2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I2" t="s">
+        <v>286</v>
+      </c>
+      <c r="J2" t="s">
+        <v>286</v>
+      </c>
+      <c r="K2" t="s">
+        <v>286</v>
+      </c>
+      <c r="L2" t="s">
+        <v>286</v>
+      </c>
+      <c r="M2" t="s">
+        <v>286</v>
+      </c>
+      <c r="N2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>170</v>
       </c>
@@ -2617,19 +5242,43 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>171</v>
+        <v>489</v>
       </c>
       <c r="D3" t="s">
-        <v>172</v>
+        <v>490</v>
       </c>
       <c r="E3" t="s">
-        <v>173</v>
+        <v>491</v>
       </c>
       <c r="F3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>492</v>
+      </c>
+      <c r="G3" t="s">
+        <v>286</v>
+      </c>
+      <c r="H3" t="s">
+        <v>286</v>
+      </c>
+      <c r="I3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J3" t="s">
+        <v>286</v>
+      </c>
+      <c r="K3" t="s">
+        <v>286</v>
+      </c>
+      <c r="L3" t="s">
+        <v>286</v>
+      </c>
+      <c r="M3" t="s">
+        <v>286</v>
+      </c>
+      <c r="N3" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>175</v>
       </c>
@@ -2640,16 +5289,40 @@
         <v>176</v>
       </c>
       <c r="D4" t="s">
-        <v>172</v>
+        <v>494</v>
       </c>
       <c r="E4" t="s">
-        <v>177</v>
+        <v>495</v>
       </c>
       <c r="F4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>496</v>
+      </c>
+      <c r="G4" t="s">
+        <v>286</v>
+      </c>
+      <c r="H4" t="s">
+        <v>286</v>
+      </c>
+      <c r="I4" t="s">
+        <v>286</v>
+      </c>
+      <c r="J4" t="s">
+        <v>286</v>
+      </c>
+      <c r="K4" t="s">
+        <v>286</v>
+      </c>
+      <c r="L4" t="s">
+        <v>286</v>
+      </c>
+      <c r="M4" t="s">
+        <v>286</v>
+      </c>
+      <c r="N4" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>179</v>
       </c>
@@ -2657,16 +5330,40 @@
         <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>180</v>
+        <v>498</v>
       </c>
       <c r="D5" t="s">
-        <v>181</v>
+        <v>499</v>
       </c>
       <c r="E5" t="s">
-        <v>182</v>
+        <v>500</v>
       </c>
       <c r="F5" t="s">
-        <v>183</v>
+        <v>501</v>
+      </c>
+      <c r="G5" t="s">
+        <v>286</v>
+      </c>
+      <c r="H5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I5" t="s">
+        <v>286</v>
+      </c>
+      <c r="J5" t="s">
+        <v>286</v>
+      </c>
+      <c r="K5" t="s">
+        <v>286</v>
+      </c>
+      <c r="L5" t="s">
+        <v>286</v>
+      </c>
+      <c r="M5" t="s">
+        <v>286</v>
+      </c>
+      <c r="N5" t="s">
+        <v>502</v>
       </c>
     </row>
   </sheetData>
@@ -2677,68 +5374,68 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" width="14"/>
+    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
+    <col bestFit="true" customWidth="true" max="3" min="3" width="14.6640625"/>
+    <col bestFit="true" customWidth="true" max="4" min="4" width="13.77734375"/>
+    <col bestFit="true" customWidth="true" max="5" min="5" width="25.88671875"/>
+    <col bestFit="true" customWidth="true" max="6" min="6" width="24.6640625"/>
+    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
+    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
+    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
+    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
+    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
+    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
+    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>184</v>
       </c>
@@ -2749,16 +5446,40 @@
         <v>185</v>
       </c>
       <c r="D2" t="s">
-        <v>186</v>
+        <v>503</v>
       </c>
       <c r="E2" t="s">
-        <v>187</v>
+        <v>504</v>
       </c>
       <c r="F2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>505</v>
+      </c>
+      <c r="G2" t="s">
+        <v>286</v>
+      </c>
+      <c r="H2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I2" t="s">
+        <v>286</v>
+      </c>
+      <c r="J2" t="s">
+        <v>286</v>
+      </c>
+      <c r="K2" t="s">
+        <v>286</v>
+      </c>
+      <c r="L2" t="s">
+        <v>286</v>
+      </c>
+      <c r="M2" t="s">
+        <v>286</v>
+      </c>
+      <c r="N2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>189</v>
       </c>
@@ -2769,16 +5490,40 @@
         <v>190</v>
       </c>
       <c r="D3" t="s">
-        <v>191</v>
+        <v>507</v>
       </c>
       <c r="E3" t="s">
-        <v>192</v>
+        <v>508</v>
       </c>
       <c r="F3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>509</v>
+      </c>
+      <c r="G3" t="s">
+        <v>286</v>
+      </c>
+      <c r="H3" t="s">
+        <v>286</v>
+      </c>
+      <c r="I3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J3" t="s">
+        <v>286</v>
+      </c>
+      <c r="K3" t="s">
+        <v>286</v>
+      </c>
+      <c r="L3" t="s">
+        <v>286</v>
+      </c>
+      <c r="M3" t="s">
+        <v>286</v>
+      </c>
+      <c r="N3" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>194</v>
       </c>
@@ -2789,16 +5534,40 @@
         <v>195</v>
       </c>
       <c r="D4" t="s">
-        <v>191</v>
+        <v>511</v>
       </c>
       <c r="E4" t="s">
-        <v>196</v>
+        <v>512</v>
       </c>
       <c r="F4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>513</v>
+      </c>
+      <c r="G4" t="s">
+        <v>286</v>
+      </c>
+      <c r="H4" t="s">
+        <v>286</v>
+      </c>
+      <c r="I4" t="s">
+        <v>286</v>
+      </c>
+      <c r="J4" t="s">
+        <v>286</v>
+      </c>
+      <c r="K4" t="s">
+        <v>286</v>
+      </c>
+      <c r="L4" t="s">
+        <v>286</v>
+      </c>
+      <c r="M4" t="s">
+        <v>286</v>
+      </c>
+      <c r="N4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>198</v>
       </c>
@@ -2806,16 +5575,40 @@
         <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>199</v>
+        <v>515</v>
       </c>
       <c r="D5" t="s">
-        <v>186</v>
+        <v>516</v>
       </c>
       <c r="E5" t="s">
-        <v>200</v>
+        <v>517</v>
       </c>
       <c r="F5" t="s">
-        <v>201</v>
+        <v>518</v>
+      </c>
+      <c r="G5" t="s">
+        <v>286</v>
+      </c>
+      <c r="H5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I5" t="s">
+        <v>286</v>
+      </c>
+      <c r="J5" t="s">
+        <v>286</v>
+      </c>
+      <c r="K5" t="s">
+        <v>286</v>
+      </c>
+      <c r="L5" t="s">
+        <v>286</v>
+      </c>
+      <c r="M5" t="s">
+        <v>286</v>
+      </c>
+      <c r="N5" t="s">
+        <v>519</v>
       </c>
     </row>
   </sheetData>
@@ -2826,53 +5619,53 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>202</v>
       </c>
@@ -2883,16 +5676,40 @@
         <v>203</v>
       </c>
       <c r="D2" t="s">
-        <v>204</v>
+        <v>520</v>
       </c>
       <c r="E2" t="s">
-        <v>205</v>
+        <v>521</v>
       </c>
       <c r="F2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>522</v>
+      </c>
+      <c r="G2" t="s">
+        <v>286</v>
+      </c>
+      <c r="H2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I2" t="s">
+        <v>286</v>
+      </c>
+      <c r="J2" t="s">
+        <v>286</v>
+      </c>
+      <c r="K2" t="s">
+        <v>286</v>
+      </c>
+      <c r="L2" t="s">
+        <v>286</v>
+      </c>
+      <c r="M2" t="s">
+        <v>286</v>
+      </c>
+      <c r="N2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>207</v>
       </c>
@@ -2903,16 +5720,40 @@
         <v>208</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>524</v>
       </c>
       <c r="E3" t="s">
-        <v>209</v>
+        <v>525</v>
       </c>
       <c r="F3" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>526</v>
+      </c>
+      <c r="G3" t="s">
+        <v>286</v>
+      </c>
+      <c r="H3" t="s">
+        <v>286</v>
+      </c>
+      <c r="I3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J3" t="s">
+        <v>286</v>
+      </c>
+      <c r="K3" t="s">
+        <v>286</v>
+      </c>
+      <c r="L3" t="s">
+        <v>286</v>
+      </c>
+      <c r="M3" t="s">
+        <v>286</v>
+      </c>
+      <c r="N3" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>211</v>
       </c>
@@ -2920,19 +5761,43 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>212</v>
+        <v>528</v>
       </c>
       <c r="D4" t="s">
-        <v>213</v>
+        <v>529</v>
       </c>
       <c r="E4" t="s">
-        <v>214</v>
+        <v>530</v>
       </c>
       <c r="F4" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>531</v>
+      </c>
+      <c r="G4" t="s">
+        <v>286</v>
+      </c>
+      <c r="H4" t="s">
+        <v>286</v>
+      </c>
+      <c r="I4" t="s">
+        <v>286</v>
+      </c>
+      <c r="J4" t="s">
+        <v>286</v>
+      </c>
+      <c r="K4" t="s">
+        <v>286</v>
+      </c>
+      <c r="L4" t="s">
+        <v>286</v>
+      </c>
+      <c r="M4" t="s">
+        <v>286</v>
+      </c>
+      <c r="N4" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>216</v>
       </c>
@@ -2940,19 +5805,43 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>217</v>
+        <v>533</v>
       </c>
       <c r="D5" t="s">
-        <v>213</v>
+        <v>534</v>
       </c>
       <c r="E5" t="s">
-        <v>218</v>
+        <v>535</v>
       </c>
       <c r="F5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+        <v>536</v>
+      </c>
+      <c r="G5" t="s">
+        <v>286</v>
+      </c>
+      <c r="H5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I5" t="s">
+        <v>286</v>
+      </c>
+      <c r="J5" t="s">
+        <v>286</v>
+      </c>
+      <c r="K5" t="s">
+        <v>286</v>
+      </c>
+      <c r="L5" t="s">
+        <v>286</v>
+      </c>
+      <c r="M5" t="s">
+        <v>286</v>
+      </c>
+      <c r="N5" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>220</v>
       </c>
@@ -2960,19 +5849,43 @@
         <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>221</v>
+        <v>538</v>
       </c>
       <c r="D6" t="s">
-        <v>222</v>
+        <v>539</v>
       </c>
       <c r="E6" t="s">
-        <v>223</v>
+        <v>540</v>
       </c>
       <c r="F6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+        <v>541</v>
+      </c>
+      <c r="G6" t="s">
+        <v>286</v>
+      </c>
+      <c r="H6" t="s">
+        <v>286</v>
+      </c>
+      <c r="I6" t="s">
+        <v>286</v>
+      </c>
+      <c r="J6" t="s">
+        <v>286</v>
+      </c>
+      <c r="K6" t="s">
+        <v>286</v>
+      </c>
+      <c r="L6" t="s">
+        <v>286</v>
+      </c>
+      <c r="M6" t="s">
+        <v>286</v>
+      </c>
+      <c r="N6" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>225</v>
       </c>
@@ -2980,19 +5893,43 @@
         <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>226</v>
+        <v>543</v>
       </c>
       <c r="D7" t="s">
-        <v>213</v>
+        <v>544</v>
       </c>
       <c r="E7" t="s">
-        <v>227</v>
+        <v>545</v>
       </c>
       <c r="F7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+      <c r="G7" t="s">
+        <v>286</v>
+      </c>
+      <c r="H7" t="s">
+        <v>286</v>
+      </c>
+      <c r="I7" t="s">
+        <v>286</v>
+      </c>
+      <c r="J7" t="s">
+        <v>286</v>
+      </c>
+      <c r="K7" t="s">
+        <v>286</v>
+      </c>
+      <c r="L7" t="s">
+        <v>286</v>
+      </c>
+      <c r="M7" t="s">
+        <v>286</v>
+      </c>
+      <c r="N7" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>229</v>
       </c>
@@ -3000,16 +5937,40 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>230</v>
+        <v>548</v>
       </c>
       <c r="D8" t="s">
-        <v>231</v>
+        <v>549</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>550</v>
       </c>
       <c r="F8" t="s">
-        <v>232</v>
+        <v>551</v>
+      </c>
+      <c r="G8" t="s">
+        <v>286</v>
+      </c>
+      <c r="H8" t="s">
+        <v>286</v>
+      </c>
+      <c r="I8" t="s">
+        <v>286</v>
+      </c>
+      <c r="J8" t="s">
+        <v>286</v>
+      </c>
+      <c r="K8" t="s">
+        <v>286</v>
+      </c>
+      <c r="L8" t="s">
+        <v>286</v>
+      </c>
+      <c r="M8" t="s">
+        <v>286</v>
+      </c>
+      <c r="N8" t="s">
+        <v>552</v>
       </c>
     </row>
   </sheetData>
@@ -3020,68 +5981,68 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" width="13.33203125"/>
+    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
+    <col bestFit="true" customWidth="true" max="3" min="3" width="24.88671875"/>
+    <col bestFit="true" customWidth="true" max="4" min="4" width="21.88671875"/>
+    <col bestFit="true" customWidth="true" max="5" min="5" width="34.88671875"/>
+    <col bestFit="true" customWidth="true" max="6" min="6" width="38.77734375"/>
+    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
+    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
+    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
+    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
+    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
+    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
+    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>233</v>
       </c>
@@ -3089,19 +6050,43 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>234</v>
+        <v>553</v>
       </c>
       <c r="D2" t="s">
-        <v>235</v>
+        <v>554</v>
       </c>
       <c r="E2" t="s">
-        <v>236</v>
+        <v>555</v>
       </c>
       <c r="F2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>556</v>
+      </c>
+      <c r="G2" t="s">
+        <v>286</v>
+      </c>
+      <c r="H2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I2" t="s">
+        <v>286</v>
+      </c>
+      <c r="J2" t="s">
+        <v>286</v>
+      </c>
+      <c r="K2" t="s">
+        <v>286</v>
+      </c>
+      <c r="L2" t="s">
+        <v>286</v>
+      </c>
+      <c r="M2" t="s">
+        <v>286</v>
+      </c>
+      <c r="N2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>238</v>
       </c>
@@ -3109,19 +6094,43 @@
         <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>239</v>
+        <v>558</v>
       </c>
       <c r="D3" t="s">
-        <v>240</v>
+        <v>559</v>
       </c>
       <c r="E3" t="s">
-        <v>241</v>
+        <v>560</v>
       </c>
       <c r="F3" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>561</v>
+      </c>
+      <c r="G3" t="s">
+        <v>286</v>
+      </c>
+      <c r="H3" t="s">
+        <v>286</v>
+      </c>
+      <c r="I3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J3" t="s">
+        <v>286</v>
+      </c>
+      <c r="K3" t="s">
+        <v>286</v>
+      </c>
+      <c r="L3" t="s">
+        <v>286</v>
+      </c>
+      <c r="M3" t="s">
+        <v>286</v>
+      </c>
+      <c r="N3" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>243</v>
       </c>
@@ -3129,16 +6138,40 @@
         <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>244</v>
+        <v>563</v>
       </c>
       <c r="D4" t="s">
-        <v>245</v>
+        <v>564</v>
       </c>
       <c r="E4" t="s">
-        <v>246</v>
+        <v>565</v>
       </c>
       <c r="F4" t="s">
-        <v>247</v>
+        <v>566</v>
+      </c>
+      <c r="G4" t="s">
+        <v>286</v>
+      </c>
+      <c r="H4" t="s">
+        <v>286</v>
+      </c>
+      <c r="I4" t="s">
+        <v>286</v>
+      </c>
+      <c r="J4" t="s">
+        <v>286</v>
+      </c>
+      <c r="K4" t="s">
+        <v>286</v>
+      </c>
+      <c r="L4" t="s">
+        <v>286</v>
+      </c>
+      <c r="M4" t="s">
+        <v>286</v>
+      </c>
+      <c r="N4" t="s">
+        <v>567</v>
       </c>
     </row>
   </sheetData>
@@ -3167,46 +6200,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3218,16 +6251,40 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>249</v>
+        <v>568</v>
       </c>
       <c r="D2" t="s">
-        <v>250</v>
+        <v>569</v>
       </c>
       <c r="E2" t="s">
-        <v>251</v>
+        <v>570</v>
       </c>
       <c r="F2" t="s">
-        <v>252</v>
+        <v>571</v>
+      </c>
+      <c r="G2" t="s">
+        <v>286</v>
+      </c>
+      <c r="H2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I2" t="s">
+        <v>286</v>
+      </c>
+      <c r="J2" t="s">
+        <v>286</v>
+      </c>
+      <c r="K2" t="s">
+        <v>286</v>
+      </c>
+      <c r="L2" t="s">
+        <v>286</v>
+      </c>
+      <c r="M2" t="s">
+        <v>286</v>
+      </c>
+      <c r="N2" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -3238,16 +6295,40 @@
         <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>254</v>
+        <v>573</v>
       </c>
       <c r="D3" t="s">
-        <v>255</v>
+        <v>574</v>
       </c>
       <c r="E3" t="s">
-        <v>251</v>
+        <v>575</v>
       </c>
       <c r="F3" t="s">
-        <v>256</v>
+        <v>576</v>
+      </c>
+      <c r="G3" t="s">
+        <v>286</v>
+      </c>
+      <c r="H3" t="s">
+        <v>286</v>
+      </c>
+      <c r="I3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J3" t="s">
+        <v>286</v>
+      </c>
+      <c r="K3" t="s">
+        <v>286</v>
+      </c>
+      <c r="L3" t="s">
+        <v>286</v>
+      </c>
+      <c r="M3" t="s">
+        <v>286</v>
+      </c>
+      <c r="N3" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -3258,16 +6339,40 @@
         <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>258</v>
+        <v>578</v>
       </c>
       <c r="D4" t="s">
-        <v>259</v>
+        <v>579</v>
       </c>
       <c r="E4" t="s">
-        <v>251</v>
+        <v>580</v>
       </c>
       <c r="F4" t="s">
-        <v>260</v>
+        <v>581</v>
+      </c>
+      <c r="G4" t="s">
+        <v>286</v>
+      </c>
+      <c r="H4" t="s">
+        <v>286</v>
+      </c>
+      <c r="I4" t="s">
+        <v>286</v>
+      </c>
+      <c r="J4" t="s">
+        <v>286</v>
+      </c>
+      <c r="K4" t="s">
+        <v>286</v>
+      </c>
+      <c r="L4" t="s">
+        <v>286</v>
+      </c>
+      <c r="M4" t="s">
+        <v>286</v>
+      </c>
+      <c r="N4" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -3278,16 +6383,40 @@
         <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>262</v>
+        <v>583</v>
       </c>
       <c r="D5" t="s">
-        <v>263</v>
+        <v>584</v>
       </c>
       <c r="E5" t="s">
-        <v>251</v>
+        <v>585</v>
       </c>
       <c r="F5" t="s">
-        <v>260</v>
+        <v>586</v>
+      </c>
+      <c r="G5" t="s">
+        <v>286</v>
+      </c>
+      <c r="H5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I5" t="s">
+        <v>286</v>
+      </c>
+      <c r="J5" t="s">
+        <v>286</v>
+      </c>
+      <c r="K5" t="s">
+        <v>286</v>
+      </c>
+      <c r="L5" t="s">
+        <v>286</v>
+      </c>
+      <c r="M5" t="s">
+        <v>286</v>
+      </c>
+      <c r="N5" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="6">
@@ -3298,16 +6427,16 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>282</v>
+        <v>588</v>
       </c>
       <c r="D6" t="s">
-        <v>283</v>
+        <v>589</v>
       </c>
       <c r="E6" t="s">
-        <v>284</v>
+        <v>590</v>
       </c>
       <c r="F6" t="s">
-        <v>285</v>
+        <v>591</v>
       </c>
       <c r="G6" t="s">
         <v>286</v>
@@ -3331,7 +6460,7 @@
         <v>286</v>
       </c>
       <c r="N6" t="s">
-        <v>286</v>
+        <v>592</v>
       </c>
     </row>
     <row r="7">
@@ -3342,16 +6471,16 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>288</v>
+        <v>593</v>
       </c>
       <c r="D7" t="s">
-        <v>289</v>
+        <v>594</v>
       </c>
       <c r="E7" t="s">
-        <v>290</v>
+        <v>595</v>
       </c>
       <c r="F7" t="s">
-        <v>291</v>
+        <v>596</v>
       </c>
       <c r="G7" t="s">
         <v>286</v>
@@ -3375,7 +6504,7 @@
         <v>286</v>
       </c>
       <c r="N7" t="s">
-        <v>286</v>
+        <v>597</v>
       </c>
     </row>
     <row r="8">
@@ -3386,16 +6515,16 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>293</v>
+        <v>598</v>
       </c>
       <c r="D8" t="s">
-        <v>294</v>
+        <v>584</v>
       </c>
       <c r="E8" t="s">
-        <v>295</v>
+        <v>599</v>
       </c>
       <c r="F8" t="s">
-        <v>296</v>
+        <v>600</v>
       </c>
       <c r="G8" t="s">
         <v>286</v>
@@ -3419,7 +6548,7 @@
         <v>286</v>
       </c>
       <c r="N8" t="s">
-        <v>286</v>
+        <v>601</v>
       </c>
     </row>
     <row r="9">
@@ -3430,16 +6559,16 @@
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>298</v>
+        <v>602</v>
       </c>
       <c r="D9" t="s">
-        <v>294</v>
+        <v>584</v>
       </c>
       <c r="E9" t="s">
-        <v>299</v>
+        <v>603</v>
       </c>
       <c r="F9" t="s">
-        <v>300</v>
+        <v>604</v>
       </c>
       <c r="G9" t="s">
         <v>286</v>
@@ -3463,7 +6592,7 @@
         <v>286</v>
       </c>
       <c r="N9" t="s">
-        <v>286</v>
+        <v>605</v>
       </c>
     </row>
     <row r="10">
@@ -3474,16 +6603,16 @@
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>302</v>
+        <v>606</v>
       </c>
       <c r="D10" t="s">
-        <v>303</v>
+        <v>607</v>
       </c>
       <c r="E10" t="s">
-        <v>304</v>
+        <v>608</v>
       </c>
       <c r="F10" t="s">
-        <v>305</v>
+        <v>609</v>
       </c>
       <c r="G10" t="s">
         <v>286</v>
@@ -3507,7 +6636,7 @@
         <v>286</v>
       </c>
       <c r="N10" t="s">
-        <v>286</v>
+        <v>610</v>
       </c>
     </row>
     <row r="11">
@@ -3518,16 +6647,16 @@
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>307</v>
+        <v>611</v>
       </c>
       <c r="D11" t="s">
-        <v>294</v>
+        <v>584</v>
       </c>
       <c r="E11" t="s">
-        <v>308</v>
+        <v>612</v>
       </c>
       <c r="F11" t="s">
-        <v>309</v>
+        <v>613</v>
       </c>
       <c r="G11" t="s">
         <v>286</v>
@@ -3551,7 +6680,7 @@
         <v>286</v>
       </c>
       <c r="N11" t="s">
-        <v>286</v>
+        <v>614</v>
       </c>
     </row>
     <row r="12">
@@ -3562,16 +6691,16 @@
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>311</v>
+        <v>615</v>
       </c>
       <c r="D12" t="s">
-        <v>294</v>
+        <v>584</v>
       </c>
       <c r="E12" t="s">
-        <v>312</v>
+        <v>616</v>
       </c>
       <c r="F12" t="s">
-        <v>309</v>
+        <v>617</v>
       </c>
       <c r="G12" t="s">
         <v>286</v>
@@ -3595,7 +6724,7 @@
         <v>286</v>
       </c>
       <c r="N12" t="s">
-        <v>286</v>
+        <v>618</v>
       </c>
     </row>
     <row r="13">
@@ -3606,16 +6735,16 @@
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>314</v>
+        <v>619</v>
       </c>
       <c r="D13" t="s">
-        <v>294</v>
+        <v>584</v>
       </c>
       <c r="E13" t="s">
-        <v>315</v>
+        <v>620</v>
       </c>
       <c r="F13" t="s">
-        <v>316</v>
+        <v>621</v>
       </c>
       <c r="G13" t="s">
         <v>286</v>
@@ -3639,7 +6768,7 @@
         <v>286</v>
       </c>
       <c r="N13" t="s">
-        <v>286</v>
+        <v>622</v>
       </c>
     </row>
     <row r="14">
@@ -3650,16 +6779,16 @@
         <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>318</v>
+        <v>623</v>
       </c>
       <c r="D14" t="s">
-        <v>319</v>
+        <v>624</v>
       </c>
       <c r="E14" t="s">
-        <v>320</v>
+        <v>625</v>
       </c>
       <c r="F14" t="s">
-        <v>321</v>
+        <v>626</v>
       </c>
       <c r="G14" t="s">
         <v>286</v>
@@ -3683,7 +6812,7 @@
         <v>286</v>
       </c>
       <c r="N14" t="s">
-        <v>286</v>
+        <v>627</v>
       </c>
     </row>
     <row r="15">
@@ -3694,16 +6823,16 @@
         <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>323</v>
+        <v>628</v>
       </c>
       <c r="D15" t="s">
-        <v>235</v>
+        <v>629</v>
       </c>
       <c r="E15" t="s">
-        <v>324</v>
+        <v>630</v>
       </c>
       <c r="F15" t="s">
-        <v>325</v>
+        <v>631</v>
       </c>
       <c r="G15" t="s">
         <v>286</v>
@@ -3727,7 +6856,7 @@
         <v>286</v>
       </c>
       <c r="N15" t="s">
-        <v>286</v>
+        <v>632</v>
       </c>
     </row>
     <row r="16">
@@ -3738,16 +6867,16 @@
         <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>327</v>
+        <v>633</v>
       </c>
       <c r="D16" t="s">
-        <v>328</v>
+        <v>634</v>
       </c>
       <c r="E16" t="s">
-        <v>329</v>
+        <v>635</v>
       </c>
       <c r="F16" t="s">
-        <v>330</v>
+        <v>636</v>
       </c>
       <c r="G16" t="s">
         <v>286</v>
@@ -3771,7 +6900,7 @@
         <v>286</v>
       </c>
       <c r="N16" t="s">
-        <v>286</v>
+        <v>637</v>
       </c>
     </row>
     <row r="17">
@@ -3782,16 +6911,16 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>332</v>
+        <v>638</v>
       </c>
       <c r="D17" t="s">
-        <v>333</v>
+        <v>639</v>
       </c>
       <c r="E17" t="s">
-        <v>334</v>
+        <v>640</v>
       </c>
       <c r="F17" t="s">
-        <v>335</v>
+        <v>641</v>
       </c>
       <c r="G17" t="s">
         <v>286</v>
@@ -3815,7 +6944,7 @@
         <v>286</v>
       </c>
       <c r="N17" t="s">
-        <v>286</v>
+        <v>642</v>
       </c>
     </row>
     <row r="18">
@@ -3826,16 +6955,16 @@
         <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>337</v>
+        <v>643</v>
       </c>
       <c r="D18" t="s">
-        <v>338</v>
+        <v>644</v>
       </c>
       <c r="E18" t="s">
-        <v>339</v>
+        <v>645</v>
       </c>
       <c r="F18" t="s">
-        <v>340</v>
+        <v>646</v>
       </c>
       <c r="G18" t="s">
         <v>286</v>
@@ -3859,7 +6988,7 @@
         <v>286</v>
       </c>
       <c r="N18" t="s">
-        <v>286</v>
+        <v>647</v>
       </c>
     </row>
     <row r="19">
@@ -3870,16 +6999,16 @@
         <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>342</v>
+        <v>648</v>
       </c>
       <c r="D19" t="s">
-        <v>343</v>
+        <v>649</v>
       </c>
       <c r="E19" t="s">
-        <v>344</v>
+        <v>650</v>
       </c>
       <c r="F19" t="s">
-        <v>345</v>
+        <v>651</v>
       </c>
       <c r="G19" t="s">
         <v>286</v>
@@ -3903,7 +7032,7 @@
         <v>286</v>
       </c>
       <c r="N19" t="s">
-        <v>286</v>
+        <v>652</v>
       </c>
     </row>
   </sheetData>
